--- a/lionsgate_library.xlsx
+++ b/lionsgate_library.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X422"/>
+  <dimension ref="A1:Y422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,11 @@
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>need</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>lead_gender</t>
         </is>
       </c>
     </row>
@@ -639,6 +644,11 @@
           <t>"The Ex" (2006) meets viewer desires for light romantic comedy entertainment, workplace humor, and schadenfreude through its premise of a man dealing with a manipulative colleague while navigating career struggles and relationship pressures. It offers escapist comedy about relatable workplace conflicts and marital challenges, appealing to audiences seeking uncomplicated, feel-good entertainment with familiar comedic actors.</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -719,6 +729,11 @@
       <c r="X3" t="inlineStr">
         <is>
           <t>"The Last Hand" is a 2008 Western drama that meets viewers' desires for classic frontier storytelling, exploring themes of redemption, mortality, and second chances. It appeals to audiences seeking character-driven narratives about an aging gambler facing his past mistakes while confronting his own death. The film satisfies needs for contemplative Westerns that focus on personal reckoning rather than action, offering emotional depth and examination of legacy and forgiveness in a dying Old West setting.</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -821,6 +836,11 @@
 The film resonates with viewers who appreciate melancholic, character-driven stories about broken people finding unexpected salvation.</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -911,6 +931,11 @@
           <t>"Affliction" meets viewers' desires for intense psychological drama and character study. It appeals to those seeking exploration of generational trauma, toxic masculinity, and the cycle of abuse in small-town America. The film satisfies audiences interested in raw, unflinching performances (particularly Nick Nolte's portrayal of a man's descent), serious adult themes, and atmospheric noir-inflected storytelling that prioritizes character depth over plot mechanics.</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -993,6 +1018,11 @@
           <t>"Serial Killing 101" (also known as "Serial Killing 4 Dummys") is a dark comedy that appeals to viewers interested in satire of true crime culture, dark humor about taboo subjects, and subversive takes on the serial killer genre. It meets desires for transgressive comedy, meta-commentary on society's fascination with serial killers, and low-budget indie filmmaking that challenges mainstream sensibilities through its mockumentary style and intentionally provocative premise.</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1063,6 +1093,11 @@
           <t>I don't have any information about a film called "Raising the Heights" in my knowledge base. Without details about this specific film, I cannot accurately describe what viewer desires or needs it meets. This may be a lesser-known, independent, or recent film that isn't widely documented, or the title may be slightly different from what I'm familiar with.</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1153,6 +1188,11 @@
           <t>"Sometimes They Come Back... for More" appeals to viewers seeking low-budget horror thrills with a military/Antarctic isolation setting. It satisfies desires for supernatural suspense, demonic possession themes, and B-movie creature effects. The film attracts fans of the "Sometimes They Come Back" franchise and those who enjoy straightforward, formulaic horror without complex narratives—offering escapist entertainment through familiar genre tropes of good versus evil in a confined, atmospheric location.</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1243,6 +1283,11 @@
           <t>"The Minus Man" meets viewers' desires for psychological complexity and ambiguity, offering a chilling character study of a soft-spoken serial killer that explores the banality of evil. It appeals to those seeking unconventional thriller narratives without gratuitous violence, instead providing unsettling introspection into a disturbed mind. The film satisfies audiences interested in morally ambiguous protagonists and atmospheric tension over conventional action, while raising questions about identity, isolation, and the hidden darkness in ordinary people.</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1333,6 +1378,11 @@
           <t># Summary: Viewer Desires and Needs Met by Dogma
 **Dogma** (1999) satisfies several viewer desires:
 1. **Intellectual stimulation** - The film engages audiences who enjoy questioning religious doctrine and exploring theological paradoxes through clever, thought-provoking humor. 2. **Irreverent comedy** - It appeals to viewers seeking bold, taboo-breaking satire that challenges sacred institutions while remaining entertaining. 3. **Action and adventure** - The plot provides excitement through its apocalyptic stakes and fantastical elements for those wanting genre entertainment. 4. **Philosophical exploration** - It meets the need for media that wrestles with faith, doubt, and the nature of belief without providing easy answers. 5. **Kevin Smith fandom** - The film serves fans of Smith's View Askewniverse with familiar characters and his signature dialogue style. 6. **Validation of doubt** - It resonates with viewers who struggle with organized religion, offering permission to question while not rejecting spirituality entirely.</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1429,6 +1479,11 @@
 The documentary appeals to both wrestling fans seeking truth about their favorite sport and general audiences interested in compelling character-driven stories about dedication and sacrifice.</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1521,6 +1576,11 @@
 **Social Commentary &amp; Critique** - Appeals to audiences seeking satirical examination of 1980s consumerism, materialism, and yuppie culture. **Dark Humor** - Provides shock value and transgressive comedy for those who enjoy provocative, boundary-pushing entertainment. **Psychological Intrigue** - Engages viewers interested in unreliable narrators and ambiguous reality, offering interpretive complexity. **Aesthetic Pleasure** - Delivers meticulous period detail, fashion, and design for those who appreciate visual style and 80s nostalgia. **Cathartic Violence** - Offers vicarious release through extreme content in a safely fictional context. **Cultural Literacy** - Allows viewers to engage with a cult classic that has become culturally significant and widely referenced. The film primarily attracts audiences seeking intelligent horror-satire that critiques capitalism while entertaining through its excessive, darkly comic approach.</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1612,6 +1672,11 @@
 *Leprechaun in the Hood* (2000) meets viewer desires for campy horror-comedy entertainment, offering absurdist humor, over-the-top violence, and self-aware B-movie charm. It appeals to fans seeking low-budget cult films that don't take themselves seriously, providing escapist fun through outrageous scenarios mixing hip-hop culture with slasher elements. The film satisfies cravings for "so bad it's good" entertainment, nostalgia for 90s direct-to-video horror, and the guilty pleasure of watching ridiculous premises executed with commitment. It also offers social commentary through satire, albeit crude, on commercialization of hip-hop and the music industry.</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1698,6 +1763,11 @@
           <t># Summary of Viewer Desires Met by "Hide and Seek"
 The film "Hide and Seek" (2005) satisfies several key viewer desires:
 **Psychological Thriller Appeal**: Provides suspense, mystery, and plot twists that keep audiences guessing about the identity of "Charlie" and the true nature of events. **Twist Ending Gratification**: Delivers a significant reveal that recontextualizes the entire narrative, appealing to viewers who enjoy being surprised and mentally engaged. **Dark Atmosphere**: Offers a creepy, unsettling mood through gothic visuals and tension, satisfying horror-adjacent thriller fans. **Parental Fear Exploration**: Taps into anxieties about child safety, trauma, and the limits of parental protection after loss. **Performance Showcase**: Features Robert De Niro and Dakota Fanning in intense dramatic roles, appealing to fans of actor-driven cinema. **Escapist Entertainment**: Provides a self-contained mystery that offers distraction and engagement for ~100 minutes without requiring prior knowledge or significant intellectual commitment.</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1797,6 +1867,11 @@
 The film primarily targets young adult audiences looking for an uncomplicated, fun romantic comedy with elements of teenage wish-fulfillment.</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1879,6 +1954,11 @@
           <t>"Lion of Oz" meets viewers' desires for family-friendly entertainment, nostalgia for the classic Oz universe, simple moral lessons about courage and friendship, colorful animation suitable for young children, and a safe, predictable adventure story with a positive message and happy ending.</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1961,6 +2041,11 @@
           <t>"The Opponent" meets viewers' desires for inspirational underdog stories, showcasing themes of redemption, perseverance, and overcoming personal struggles. The film appeals to those who enjoy sports dramas, particularly boxing narratives, while addressing deeper emotional needs through its portrayal of a flawed protagonist seeking second chances and personal transformation. It satisfies audiences looking for gritty, character-driven stories about resilience in the face of adversity.</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2031,6 +2116,11 @@
           <t>I don't have specific information about a film titled "Women in Film" to provide an accurate summary of what viewer desires or needs it meets. If you're referring to a documentary or specific film about women's roles in cinema, please provide more details such as the release year or director, and I can offer a more helpful response.</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2119,6 +2209,11 @@
       <c r="X19" t="inlineStr">
         <is>
           <t>The film "Bully" (2001) meets viewers' desires for unflinching, provocative cinema that explores dark aspects of human nature. It satisfies those interested in true crime stories, as it's based on the real murder of Bobby Kent. The film appeals to audiences seeking controversial content that examines youth violence, moral ambiguity, and suburban dysfunction without romanticizing or sanitizing the subject matter. It also attracts viewers interested in Larry Clark's transgressive filmmaking style and those wanting to examine how group dynamics and abuse can escalate to extreme violence.</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2219,6 +2314,11 @@
 If you're referring to a different film titled "Cabin Pressure," please note that information may vary.</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2299,6 +2399,11 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>"All Over the Guy" (2001) meets viewer desires for romantic comedy with LGBTQ+ representation, offering a relatable story about modern dating, relationship anxieties, and finding love despite personal baggage. It satisfies needs for lighthearted entertainment that validates queer experiences, explores neurotic but endearing characters, and provides both humor and emotional resonance for audiences seeking gay-themed rom-coms with mainstream appeal.</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2355,6 +2460,7 @@
           <t>"Christy: A Change of Seasons" meets viewers' desires for wholesome family entertainment, inspirational storytelling, and nostalgic continuation of the beloved "Christy" TV series. The film appeals to audiences seeking uplifting moral messages, clean romance, faith-based content, and stories about personal growth and community values set in historical Appalachia. It satisfies fans' longing to revisit familiar characters and resolve storylines from the original series.</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2447,6 +2553,11 @@
 **Drama and Conflict**: Viewers seeking intense emotional drama find satisfaction in the film's exploration of jealousy, betrayal, and manipulation among teenagers. **Contemporary Relevance**: The adaptation translates classic themes of racism, insecurity, and toxic relationships into a modern American setting that resonates with younger audiences. **Forbidden/Controversial Content**: The film addresses taboo subjects like interracial relationships, sexual manipulation, and teen violence, appealing to viewers interested in edgy, provocative material. **Psychological Thriller Elements**: The slow psychological unraveling of the protagonist satisfies audiences who enjoy watching complex character deterioration and manipulation. **Social Commentary**: The film meets the desire for narratives that explore racial tensions, social hierarchies, and the darker aspects of competitive environments like sports culture. **Tragic Romance**: Viewers drawn to doomed love stories find the tragic relationship at the film's core emotionally compelling.</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2523,6 +2634,11 @@
       <c r="X24" t="inlineStr">
         <is>
           <t>"One Eyed King" meets viewers' desires for gritty crime drama, exploring themes of loyalty, survival, and moral ambiguity in the criminal underworld. It appeals to those seeking intense character-driven narratives about brotherhood, redemption, and the consequences of violence, while satisfying audiences interested in underground fight culture and the complexities of choosing between family bonds and personal ethics.</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2623,6 +2739,11 @@
 The film appeals to those wanting visually ambitious, atmospheric entertainment with mystery-thriller storytelling.</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2721,6 +2842,11 @@
 The film appeals to those interested in Old Hollywood history, murder mysteries, and the hidden lives of iconic figures.</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2805,6 +2931,11 @@
       <c r="X27" t="inlineStr">
         <is>
           <t>"Two Degrees" meets viewers' desires for environmental awareness and climate change education by dramatizing the potential consequences of global temperature rise. It fulfills needs for urgent storytelling about sustainability, scientific literacy regarding climate impacts, and motivation for environmental action. The film appeals to those seeking thought-provoking content about humanity's future and our relationship with the planet.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2904,6 +3035,11 @@
 The movie provides uncomplicated, feel-good entertainment without demanding deep engagement, targeting audiences seeking casual comedy with familiar music industry personalities.</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2996,6 +3132,11 @@
 **Emotional catharsis** - The film provides a profound emotional release through its exploration of grief, loneliness, and redemption. **Complex character study** - Viewers seeking depth appreciate watching flawed, prejudiced characters undergo genuine transformation and growth. **Raw authenticity** - The unflinching portrayal of difficult subjects like racism, loss, and human connection appeals to audiences wanting honest, adult drama. **Powerful performances** - The film satisfies appreciation for exceptional acting, particularly Halle Berry's Oscar-winning performance. **Social commentary** - It addresses racial tensions and systemic issues, meeting the need for thought-provoking content about American society. **Hope and redemption** - Despite its darkness, the film offers the possibility of healing and human connection across seemingly insurmountable divides.</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3054,6 +3195,7 @@
           <t>"Christy - A New Beginning" meets viewers' desires for inspirational drama, romantic storylines, and wholesome family entertainment. The film appeals to those seeking stories about personal growth, faith-based values, and overcoming challenges in a historical setting. It satisfies fans of the original "Christy" series who wanted continuation of the beloved characters' journeys, while also providing nostalgia and comfort through its portrayal of a dedicated teacher making a difference in an Appalachian community during the early 1900s.</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3140,6 +3282,11 @@
           <t>"Narc" meets viewers' desires for gritty, realistic crime drama with morally complex characters. It satisfies needs for intense psychological tension, authentic police procedural storytelling, and exploration of themes like corruption, loyalty, and the personal costs of undercover work. The film appeals to those seeking dark, visceral cinema with strong performances and ambiguous morality rather than clear-cut heroes and villains.</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3236,6 +3383,11 @@
 The film appeals to viewers who enjoy thoughtful horror that blurs the line between religious faith and madness, leaving them questioning their own assumptions about truth and morality.</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3328,6 +3480,11 @@
 **Artistic inspiration and visual beauty** - The film's vibrant cinematography and recreation of Frida Kahlo's surrealist paintings satisfy viewers' desire for aesthetic pleasure and creative stimulation. **Biographical curiosity** - It fulfills interest in learning about the life of an iconic artist, particularly her tumultuous relationship with Diego Rivera and her physical suffering. **Emotional catharsis** - Viewers experience deep emotional engagement through Frida's pain, passion, and resilience in the face of physical disability and personal betrayal. **Representation and empowerment** - The film meets needs for seeing a strong, unconventional female protagonist who defied social norms regarding gender, sexuality, and physical ability. **Cultural appreciation** - It satisfies interest in Mexican culture, art history, and the revolutionary period of early 20th-century Mexico. **Inspiration through adversity** - Viewers find motivation in Frida's transformation of suffering into artistic triumph, meeting needs for hope and</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3418,6 +3575,11 @@
           <t>"The Rules of Attraction" appeals to viewers seeking a darkly satirical exploration of college life, casual relationships, and youth hedonism. The film satisfies desires for provocative, non-linear storytelling, morally ambiguous characters, and unflinching portrayals of sex, drugs, and emotional disconnection among privileged young adults. It attracts audiences interested in stylish, experimental filmmaking and cynical commentary on superficiality and the search for meaning in a morally hollow environment.</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3510,6 +3672,11 @@
 **Escapism and thrills** - The intricate con artist plot provides excitement and tension as audiences watch elaborate schemes unfold. **Intellectual engagement** - Viewers enjoy piecing together the twists, reveals, and double-crosses in the complex narrative structure. **Wish fulfillment** - The film appeals to fantasies about outsmarting the system and living dangerously outside conventional society. **Stylish entertainment** - Slick cinematography, sharp dialogue, and charismatic performances (particularly Edward Burns and Dustin Hoffman) satisfy desires for cool, polished filmmaking. **Justice and comeuppance** - The story delivers satisfaction through revenge plots and criminals getting their due, fulfilling moral expectations despite the antihero protagonists.</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3596,6 +3763,11 @@
           <t>"Student Seduction" appeals to viewers interested in Lifetime-style psychological thrillers featuring forbidden relationship dynamics, power imbalances, and cautionary tales. It satisfies desires for dramatic tension, moral conflict, and the voyeuristic intrigue of taboo scenarios, while also serving as a warning narrative about manipulation and obsession in educational settings.</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3686,6 +3858,11 @@
           <t>"Lucky 7" is a 2003 TV movie about a group of gas station workers who win the lottery, appealing to viewers' fantasies about sudden wealth and financial freedom. The film meets desires for escapism, wish-fulfillment, and exploring themes of loyalty, friendship, and how money affects relationships. It offers feel-good entertainment while examining moral choices when ordinary people experience life-changing fortune.</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3782,6 +3959,11 @@
 - **Cultural curiosity**: A glimpse into royal life and traditions, even if fictionalized</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3873,6 +4055,11 @@
 *The Day After Tomorrow* meets viewer desires for spectacular disaster entertainment, featuring dramatic special effects of catastrophic weather events and global destruction. It satisfies the appeal of survival narratives where ordinary people face extraordinary circumstances, while also tapping into anxieties about climate change and environmental consequences. The film provides escapist entertainment through edge-of-your-seat action sequences, emotional family drama centered on a father's quest to save his son, and the cathartic experience of witnessing humanity unite against a common threat. It also offers the reassurance of human resilience and hope amid apocalyptic scenarios.</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3963,6 +4150,11 @@
           <t>**Cube Zero** appeals to viewers who enjoy science fiction thrillers with psychological and philosophical elements. It satisfies desires for mystery and puzzle-solving as characters navigate deadly traps while uncovering the sinister purpose behind the Cube. The film meets needs for dystopian commentary on authority and dehumanization, offers visceral horror through creative death scenes, and provides the intellectual satisfaction of exploring themes about free will, institutional corruption, and moral choice. Fans of the Cube franchise also get backstory revealing the system's operators and origins.</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4051,6 +4243,11 @@
       <c r="X41" t="inlineStr">
         <is>
           <t>"The Final Cut" (2004) meets viewers' desires for thought-provoking science fiction that explores themes of memory, identity, and mortality. It satisfies those interested in ethical dilemmas surrounding technology and surveillance, particularly the concept of recording one's entire life through implanted memory chips. The film appeals to audiences who enjoy cerebral thrillers with noir elements, Robin Williams in a dramatic role, and dystopian narratives that examine privacy, truth, and the malleability of personal history.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4150,6 +4347,11 @@
 - **Performance showcase** - satisfying appreciation for Spacey's singing, acting, and directorial talents in a passion project</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4240,6 +4442,11 @@
           <t># Viewer Desires Met by "Diary of a Mad Black Woman"
 **Diary of a Mad Black Woman** fulfills several key viewer needs:
 1. **Emotional catharsis** - The film allows audiences to experience and release feelings around betrayal, heartbreak, and recovery through the protagonist's journey. 2. **Justice and vindication** - Viewers see a wronged woman gain revenge and empowerment after her husband's infidelity and mistreatment. 3. **Inspirational redemption** - The story offers hope through themes of forgiveness, faith, and personal transformation. 4. **Cultural representation** - It provides Black audiences with relatable characters, family dynamics, and community experiences often underrepresented in mainstream cinema. 5. **Comic relief** - Madea's humor provides entertainment and lightens heavy dramatic themes. 6. **Romantic wish-fulfillment** - The film delivers a satisfying second-chance love story with a caring, supportive partner. 7. **Moral affirmation** - It reinforces values around faith, family, and the consequences of one's actions.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4335,6 +4542,11 @@
 The film appeals to horror fans wanting both creature features and character-driven psychological terror.</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4412,6 +4624,11 @@
         <is>
           <t># Summary
 The film *American Psycho: From Book to Screen* meets viewers' desires for behind-the-scenes insight into the adaptation process, satisfying curiosity about how controversial source material was translated to film. It appeals to fans seeking deeper understanding of creative decisions, censorship challenges, and the cultural impact of transforming Bret Easton Ellis's provocative novel into a cinematic experience. The documentary fulfills intellectual interest in filmmaking craft while providing context for one of cinema's most divisive satirical works.</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4511,6 +4728,11 @@
 - **Cult identity** - Fulfills the need to belong to a niche fan community that appreciates controversial horror cinema</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4595,6 +4817,11 @@
       <c r="X47" t="inlineStr">
         <is>
           <t>"Vampire Assassin" appeals to viewers seeking low-budget action-horror entertainment, combining martial arts fight sequences with vampire mythology. It satisfies desires for straightforward genre thrills, featuring a revenge-driven protagonist, supernatural elements, and combat choreography. The film caters to fans of direct-to-video B-movies who enjoy blending Eastern martial arts with Western horror tropes, offering unpretentious escapist entertainment without requiring significant intellectual investment.</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4694,6 +4921,11 @@
 - **Cathartic release**: The extreme scenarios allow viewers to experience danger and mortality from a safe distance</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4756,6 +4988,11 @@
           <t>I don't have any information about a film called "Full Disclosure Report" in my knowledge base. This title doesn't match any widely known documentary or feature film I'm aware of. It's possible this is a lesser-known independent film, a corporate/educational video, or perhaps the title is slightly different from what you've provided. Without access to information about this specific work, I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4828,6 +5065,11 @@
       <c r="X50" t="inlineStr">
         <is>
           <t>"In The Mix" meets viewer desires for lighthearted entertainment through its combination of romantic comedy, action, and music. The film appeals to fans of Usher and those seeking an escapist story featuring romance, humor, celebrity appeal, and a hip-hop/R&amp;B soundtrack. It satisfies audiences looking for a formulaic but enjoyable mix of genres with a charismatic lead, cross-cultural romance themes, and feel-good entertainment that doesn't require deep intellectual engagement.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4929,6 +5171,11 @@
 - **Spiritual uplift** - Faith-based themes offer hope and redemption</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5019,6 +5266,11 @@
           <t>The film "Minotaur" (2006) meets viewer desires for dark fantasy and mythology-based horror, offering graphic violence, creature effects, and exploitation elements including sexual content. It appeals to audiences seeking B-movie entertainment that combines ancient Greek mythology with horror genre conventions, featuring the classic monster-in-a-labyrinth premise with added gore and adult themes typical of direct-to-video fantasy horror films.</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5109,6 +5361,11 @@
           <t>"Skinwalkers" (2006) meets viewer desires for supernatural horror action, combining werewolf mythology with Western aesthetics. It appeals to audiences seeking creature-feature thrills, good-versus-evil conflict, and dark fantasy elements with gunfights and transformation effects. The film satisfies fans of B-movie horror who enjoy lycanthrope lore and straightforward monster action without demanding complex narratives.</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5185,6 +5442,11 @@
       <c r="X54" t="inlineStr">
         <is>
           <t>"Hostel Dissected" is a documentary that meets viewers' desires for behind-the-scenes insights into horror filmmaking. It satisfies curiosity about special effects creation, directorial vision, and the production process of the controversial horror film "Hostel." The documentary appeals to film students, horror enthusiasts, and fans interested in understanding how shocking imagery is crafted and the artistic intentions behind extreme horror cinema.</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5287,6 +5549,11 @@
 The film appeals to audiences seeking both entertainment and meaningful life lessons about presence, purpose, and personal transformation.</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5369,6 +5636,7 @@
           <t>Ultimate Avengers 2 meets viewer desires for superhero action and spectacle, team dynamics and character interactions among popular Marvel heroes, escapist entertainment with high-stakes conflict (alien invasion), continuation of storylines from the first film, and the introduction of Black Panther and Wakanda to animated Marvel content. It appeals to fans seeking straightforward good-vs-evil narratives with familiar comic book characters in an accessible animated format.</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5460,6 +5728,11 @@
 The film appeals to niche audiences wanting inventive, visually creative animated content that doesn't take itself seriously.</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5558,6 +5831,11 @@
 - **Novelty** from its unique high-concept premise (man must keep adrenaline up to survive)</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5646,6 +5924,11 @@
       <c r="X59" t="inlineStr">
         <is>
           <t>"Dorm Daze 2" meets viewer desires for lighthearted escapism through broad comedy, sexual humor, and party atmosphere typical of teen/college comedies. It appeals to audiences seeking low-stakes entertainment with physical comedy, romantic misunderstandings, and attractive young cast members in a tropical resort setting. The film caters to fans of the original who want familiar characters and formulaic but uncomplicated humor without demanding emotional investment or intellectual engagement.</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5738,6 +6021,11 @@
 The film primarily attracts audiences seeking meaning through political engagement, cultural history, and the intersection of art and activism.</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5831,6 +6119,11 @@
 **Workplace humor** - Exaggerated retail employee experiences offer cathartic comedy for anyone who's worked in service industries. **Star appeal** - Features recognizable comedy actors (Dane Cook, Dax Shepard, Jessica Simpson) during their peak popularity period. **Simple wish-fulfillment** - The fantasy that workplace success directly translates to romantic success and that minimal effort can lead to rewards.</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5917,6 +6210,11 @@
           <t>"Dark Ride" (2006) meets viewer desires for slasher horror thrills through its atmospheric amusement park setting, featuring a masked killer, jump scares, gore effects, and a group of young people being stalked in an isolated dark ride attraction. It appeals to fans seeking nostalgic early 2000s horror conventions, creepy carnival aesthetics, and straightforward survival suspense with practical kills and a mysterious villain backstory.</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6006,6 +6304,11 @@
         <is>
           <t># Summary
 *Fierce People* appeals to viewers interested in coming-of-age dramas that explore class conflict, dysfunctional family dynamics, and the dark underbelly of wealth and privilege. The film meets desires for psychological character studies featuring a teenager's loss of innocence, complex moral ambiguity, and observations about how the ultra-rich operate as their own insular "tribe." It attracts audiences seeking provocative, darker indie fare with themes of manipulation, corruption, and social commentary on American aristocracy.</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6106,6 +6409,11 @@
 The film combines visceral horror with deeper thematic content about redemption and consequences.</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6199,6 +6507,11 @@
 The film serves both devoted fans seeking deeper understanding and newcomers wanting to explore his cultural significance.</t>
         </is>
       </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6296,6 +6609,11 @@
 - **Simple moral lessons** - Clear messages about self-determination and challenging expectations for younger viewers</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6380,6 +6698,11 @@
 **Escapism and power fantasy** - Audiences experience vicarious empowerment through Tony Stark's transformation into a technologically superior hero who overcomes physical vulnerability. **Action and spectacle** - The film delivers exciting combat sequences, advanced weaponry, and visual effects that satisfy the appetite for entertainment and adrenaline. **Hero's journey** - Viewers connect with Stark's redemptive arc from self-centered industrialist to responsible protector, fulfilling the need for inspirational character growth. **Good vs. evil narrative** - The clear moral conflict between Iron Man and the Mandarin provides satisfying resolution and justice, meeting the desire for order and righteousness. **Technological wonder** - The film appeals to fascination with innovation, engineering, and futuristic possibilities through its depiction of advanced armor and gadgetry.</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6470,6 +6793,11 @@
           <t>"Daddy's Little Girls" meets viewers' desires for an uplifting family drama that addresses real-world struggles including single parenthood, custody battles, class differences, and romantic redemption. The film appeals to audiences seeking authentic African-American representation, faith-based themes, and a heartwarming story about a hardworking father fighting to protect his daughters while finding unexpected love. It satisfies the need for feel-good entertainment that balances serious social issues with hope and positive resolution.</t>
         </is>
       </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6550,6 +6878,11 @@
 **Emotional satisfaction** - It provides an uplifting, feel-good narrative about unlikely alliances and triumph over adversity. **Social justice appeal** - It satisfies desires for stories about activism, solidarity, and standing up for marginalized communities. **Historical interest** - It educates viewers about a lesser-known true story from 1980s Britain, combining LGBTQ+ history with labor movement history. **Humor and heart** - It balances serious themes with comedy, warmth, and human connection. **Representation** - It provides meaningful LGBTQ+ representation and celebrates diverse communities working together. **Inspiration** - It demonstrates how ordinary people can make a difference, meeting viewers' desire for hope and empowerment.</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6640,6 +6973,11 @@
           <t>"The Condemned" meets viewers' desires for intense action and violence, survival drama, social commentary on reality TV and media exploitation, straightforward good-vs-evil conflict, and visceral entertainment through its premise of death row inmates forced to fight to the death on a remote island while being broadcast online.</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6702,6 +7040,11 @@
           <t>I don't have any information about a film called "Envy Girls" in my knowledge base. Without being able to verify this film exists or access details about its content, I cannot accurately describe what viewer desires or needs it might meet.</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6789,6 +7132,11 @@
 The film "Catacombs" (2007) appeals to viewers seeking visceral thrills through claustrophobic horror set in the real Paris catacombs. It satisfies desires for atmospheric tension, survival horror, and the exploration of dark, forbidden spaces. The movie provides jump scares, a maze-like chase narrative, and psychological terror that appeals to audiences who enjoy feeling trapped alongside vulnerable protagonists. It also offers a twist ending that rewards viewers who appreciate narrative misdirection and unreliable perspectives in horror storytelling.</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6880,6 +7228,11 @@
 Hostel: Part II meets viewer desires for intense horror thrills, graphic gore, and shocking violence. It appeals to audiences seeking extreme content, visceral scares, and transgressive entertainment that pushes boundaries. The film also satisfies curiosities about dark human nature, provides cathartic release through fear responses, and offers escapism into a nightmarish scenario. Additionally, it caters to fans of the torture horror subgenre who appreciate creative kill sequences and sadistic suspense.</t>
         </is>
       </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6960,6 +7313,11 @@
 5. **Sports entertainment** - NASCAR fans satisfy their passion for racing culture and high-performance competition</t>
         </is>
       </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7048,6 +7406,11 @@
       <c r="X75" t="inlineStr">
         <is>
           <t>The film "Bratz" (2007) meets viewer desires for escapist teen fantasy, female friendship narratives, and wish-fulfillment through fashion and popularity. It appeals to young audiences seeking validation of individuality and self-expression while providing colorful, music-driven entertainment. The movie satisfies the need for relatable coming-of-age stories about navigating cliques, staying true to oneself, and overcoming social pressures in high school, all wrapped in a glamorous, aspirational package that echoes the doll brand's emphasis on style and confidence.</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7137,6 +7500,11 @@
 - **Action and humor balance** - Delivers exciting magical combat sequences mixed with wit and comedy that keeps the tone entertaining rather than overly serious
 - **Intellectual stimulation** - Explores concepts of time, reality, and Eastern philosophy in accessible ways that feel thought-provoking without being demanding
 - **Underdog triumph** - Shows a broken man rebuilding himself through determination, meeting the universal desire to see perseverance rewarded</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7237,6 +7605,11 @@
 The film delivers straightforward genre entertainment for action fans seeking visceral thrills and dramatic confrontations.</t>
         </is>
       </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7329,6 +7702,11 @@
 **Moral Complexity**: The film provides nuanced characters rather than simple good/evil archetypes, particularly in the relationship between rancher Dan Evans and outlaw Ben Wade, appealing to audiences seeking psychological depth. **Tension and Suspense**: The race-against-time premise creates sustained dramatic tension as Evans must get Wade to the train, fulfilling desires for excitement and edge-of-your-seat engagement. **Masculine Identity Themes**: It explores concepts of honor, redemption, and what defines a "real man," resonating with viewers interested in character-driven explorations of masculinity. **Classic Western Aesthetics**: The film delivers traditional Western pleasures—gunfights, sweeping landscapes, and frontier justice—while modernizing the genre's sensibilities. **Father-Son Dynamics**: Dan's struggle to earn his son's respect adds emotional stakes that satisfy viewers seeking family drama and personal redemption arcs. **Unpredictability**: The evolving dynamic between captor and captive keeps audiences guessing</t>
         </is>
       </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7419,6 +7797,11 @@
           <t>"Highlander: The Source" attempts to meet viewer desires for fantasy action, immortal warrior mythology, and continuation of the Highlander franchise lore. It targets fans seeking answers about the origin of immortals' powers (the "Source"), while providing sword fights, supernatural elements, and post-apocalyptic adventure. The film aims to satisfy longstanding franchise followers wanting closure to mythological questions, though it was generally poorly received by critics and audiences.</t>
         </is>
       </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7509,6 +7892,11 @@
           <t>"Good Luck Chuck" meets viewer desires for escapist romantic comedy entertainment, wish-fulfillment fantasy (the premise that sleeping with the protagonist leads to finding true love), sexual humor and attractive cast members, and the comforting formula of a predictable happy ending where the commitment-phobic protagonist overcomes his fears to find lasting love.</t>
         </is>
       </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7597,6 +7985,11 @@
       <c r="X81" t="inlineStr">
         <is>
           <t>Saw IV meets viewer desires for intense psychological thrills, complex puzzle-solving narratives, and graphic horror spectacle. It provides the satisfaction of piecing together non-linear timelines and discovering shocking plot twists, while delivering the franchise's signature gruesome "trap" sequences that appeal to fans seeking visceral, extreme content. The film also offers closure and backstory for the Jigsaw character, satisfying audience curiosity about the villain's origins and motivations.</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7698,6 +8091,11 @@
 The film fundamentally offers escapist empowerment through a wronged warrior's justified rebellion.</t>
         </is>
       </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7793,6 +8191,11 @@
 4. **Cultural curiosity** - Asian horror aesthetics and atmosphere appeal to those interested in Eastern filmmaking traditions
 5. **Emotional catharsis** - The protagonist's journey from blindness to frightening sight provides dramatic tension and resolution
 6. **Existential contemplation** - Themes about death, the afterlife, and what lies beyond our normal perception satisfy philosophical curiosity</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7893,6 +8296,11 @@
 The film appeals to audiences who enjoy intelligent crime thrillers with historical intrigue and underdog narratives.</t>
         </is>
       </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7964,6 +8372,7 @@
 *Rituales de Sangre* meets viewer desires for true crime content, morbid curiosity about occult practices, and understanding extreme human behavior. The film satisfies needs for shock value, cautionary tales about cult manipulation, and insight into a notorious criminal case. It appeals to audiences interested in drug cartel violence, ritual sacrifice, and the intersection of religion and crime, while providing a sense of moral resolution through the eventual capture and exposure of the perpetrators.</t>
         </is>
       </c>
+      <c r="Y85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8060,6 +8469,11 @@
 - **Visual spectacle**: Delivers colorful, fantastical imagery of mystical Chinese landscapes, costumes, and supernatural elements
 - **Comedy and entertainment**: Blends humor with action through the chemistry between Chan and Li's contrasting characters
 The film essentially meets the desire for an entertaining, accessible martial arts fantasy adventure with star power and crowd-pleasing action.</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8154,6 +8568,11 @@
 The film provides wholesome entertainment that reassures parents while engaging children with themes of discovery, cooperation, and personal growth.</t>
         </is>
       </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8244,6 +8663,11 @@
           <t>"Garden Party" is a 2017 animated short film that meets viewers' desires for visually stunning CGI artistry, dark humor, and thriller-like suspense. The film satisfies those seeking thought-provoking narratives that subvert expectations, as it tells a story from the perspective of amphibians discovering a sinister mystery in an abandoned mansion. It appeals to audiences who appreciate horror elements delivered through unconventional storytelling, technical excellence in animation, and narratives that reward careful attention to environmental storytelling details.</t>
         </is>
       </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8334,6 +8758,11 @@
           <t>"Bangkok Dangerous" meets viewer desires for action-thriller entertainment, featuring intense gunfights, assassin intrigue, and exotic Bangkok locations. It appeals to audiences seeking escapist violence, romantic subplot elements, and the star power of Nicolas Cage in a crime drama with themes of redemption and moral conflict.</t>
         </is>
       </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8422,6 +8851,11 @@
       <c r="X90" t="inlineStr">
         <is>
           <t>"Disaster Movie" appeals to viewers seeking lowbrow comedy through pop culture parody, slapstick humor, and crude jokes. It targets audiences who enjoy recognizing references to recent movies and celebrities, want mindless entertainment without complex plots, and appreciate gross-out humor and physical comedy. The film meets the desire for easy-to-watch, undemanding content that requires minimal attention or critical thinking.</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8513,6 +8947,11 @@
 6. **Animation Appeal** - Meets the desire for animated superhero content, which was less common for Marvel properties at the time of release</t>
         </is>
       </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8604,6 +9043,11 @@
 *My Best Friend's Girl* appeals to viewers seeking escapist romantic comedy entertainment with raunchy humor. It satisfies desires for wish-fulfillment fantasy (the "bad boy" who changes), comedic relationship dynamics, and the comfort of predictable genre conventions where love ultimately triumphs. The film also meets needs for light emotional engagement without serious commitment, featuring attractive leads in amusing situations that explore the contrast between superficial dating behavior and genuine connection. Its crude humor and sexual content appeal to audiences seeking adult-oriented comedy rather than family-friendly fare.</t>
         </is>
       </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8684,6 +9128,11 @@
       <c r="X93" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Divine Confusion" in my knowledge base. Without access to details about this specific film, I cannot accurately describe what viewer desires or needs it meets. This may be an obscure, independent, or recent film that isn't widely documented, or it may be known by a different title.</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8781,6 +9230,11 @@
 - **Emotional connection**: Themes of family, faith, and community resonate with those seeking heartfelt seasonal viewing
 - **Escapism**: A picturesque, idealized world that offers respite from daily stress
 - **Affirmation of values**: Reinforces positive messages about perseverance, creativity, and the importance of home and relationships</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8879,6 +9333,11 @@
 The film appeals primarily to audiences who value boundary-pushing art, theatrical presentation, and belonging to specialized fan communities.</t>
         </is>
       </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8974,6 +9433,11 @@
 - **Escapism through carnage** - The exaggerated violence creates distance from reality, allowing guilt-free entertainment through fictional mayhem</t>
         </is>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9058,6 +9522,11 @@
       <c r="X97" t="inlineStr">
         <is>
           <t>"The Legend of Bloody Mary" meets viewer desires for supernatural horror thrills, urban legend exploration, and teen-oriented scares. The film appeals to audiences seeking familiar horror tropes like cursed rituals, vengeful spirits, and group dynamics among young protagonists facing supernatural consequences. It satisfies the need for accessible, formulaic horror entertainment with jump scares and the nostalgic appeal of the Bloody Mary folklore that many viewers remember from childhood.</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9154,6 +9623,11 @@
 The film targets audiences wanting a flashy, visually driven experience rather than narrative depth.</t>
         </is>
       </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9245,6 +9719,11 @@
 "Tenderness" (2009) meets viewer desires for psychological thriller content that explores dark, complex themes. The film appeals to audiences interested in morally ambiguous characters, particularly through its focus on a troubled teen killer and an obsessed detective. It satisfies the need for suspense and tension while examining themes of manipulation, obsession, and the darker aspects of human nature. The movie also attracts viewers drawn to crime dramas with psychological depth and those interested in exploring the intersection of danger and misguided connection between damaged individuals.</t>
         </is>
       </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9335,6 +9814,11 @@
           <t># My Bloody Valentine: Viewer Desires and Needs Met
 **My Bloody Valentine** (1981) satisfies several key viewer desires:
 **Thrill and Fear**: The film delivers genuine scares and suspense through its slasher format, giving audiences controlled exposure to danger and adrenaline rushes in a safe environment. **Mystery and Problem-Solving**: The whodunit element engages viewers intellectually as they try to identify the killer before the reveal. **Transgression and Taboo**: The film allows viewers to vicariously experience socially forbidden acts and violence without real-world consequences. **Nostalgia and Tradition**: For horror fans, it fulfills the desire for classic slasher conventions while offering a unique Valentine's Day setting that subverts romantic expectations. **Social Bonding**: As a cult classic, it provides shared cultural experience for horror enthusiasts and opportunities for communal viewing experiences. **Catharsis**: The violent content offers emotional release and a way to process fears about mortality, relationships, and small-town claustrophobia in a symbolic framework.</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9428,6 +9912,11 @@
 - **Quick entertainment** - Compact runtime (45 minutes) for efficient viewing</t>
         </is>
       </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9519,6 +10008,11 @@
 The film primarily caters to action-oriented fans seeking pure superhero spectacle.</t>
         </is>
       </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9607,6 +10101,11 @@
       <c r="X103" t="inlineStr">
         <is>
           <t>"New in Town" meets viewer desires for lighthearted romantic comedy escapism, featuring a fish-out-of-water story where a corporate executive from Miami adapts to small-town Minnesota life and finds love. The film satisfies needs for feel-good entertainment, predictable romance, cultural clash humor, and themes of personal transformation, community values, and choosing authentic connection over career ambition.</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9687,6 +10186,11 @@
 The documentary satisfies both casual viewers seeking entertainment value and devoted fans wanting comprehensive insight into Barker's multifaceted career as writer, director, and visual artist.</t>
         </is>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9782,6 +10286,11 @@
 4. **Schadenfreude and social commentary** - Offers commentary on economic struggles during the 2008 recession, letting viewers laugh at characters in similarly difficult circumstances
 5. **Easy, mindless entertainment** - Delivers simple, predictable comedy requiring minimal intellectual engagement
 The film primarily targets young adults seeking irreverent humor and anyone with restaurant work experience looking for relatable comedy about workplace dysfunction.</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9882,6 +10391,11 @@
 The film meets the desire for horror that balances supernatural scares with relatable human struggle and emotional stakes.</t>
         </is>
       </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9972,6 +10486,11 @@
           <t>Crank: High Voltage meets viewer desires for pure adrenaline-fueled escapism, over-the-top action spectacle, dark comedy, and transgressive entertainment that breaks conventional filmmaking rules. It appeals to audiences seeking non-stop kinetic energy, absurdist humor, cartoonish violence without serious consequences, and a visceral, no-holds-barred cinematic experience that prioritizes shock value and outrageous set pieces over narrative coherence or realism.</t>
         </is>
       </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10040,6 +10559,11 @@
       <c r="X108" t="inlineStr">
         <is>
           <t>"Frankenhood" (2009) is a horror-comedy parody that appeals to viewers seeking low-budget, campy entertainment with crude humor, urban comedy elements, and a playful twist on classic Frankenstein themes. It targets audiences looking for undemanding, irreverent content that blends horror movie tropes with street comedy, offering escapist entertainment without requiring serious intellectual engagement.</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10140,6 +10664,11 @@
 - **Genre satisfaction** - Delivers sci-fi/action conventions with a cyberpunk edge</t>
         </is>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10231,6 +10760,11 @@
 *Saw VI* appeals to viewers seeking intense horror thrills, moral dilemmas about justice and corruption, and cathartic revenge fantasies. The film specifically targets the healthcare insurance industry's greed, satisfying audiences' desire to see corrupt systems punished. It also meets fans' expectations for the franchise's signature elaborate traps, plot twists, and gore, while providing closure to ongoing storylines. The film taps into economic anxieties (released during the 2008 financial crisis) by depicting institutional villains facing brutal consequences, offering visceral satisfaction to viewers frustrated with systemic injustice.</t>
         </is>
       </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10317,6 +10851,11 @@
           <t>"Summer's Blood" appeals to horror fans seeking visceral thrills through its slasher elements, including violence, gore, and suspense. It satisfies desires for dark psychological content exploring twisted family dynamics and captivity scenarios, while offering the cathartic experience of watching a victim-turned-survivor fight back against her tormentors. The film also caters to audiences interested in gritty, low-budget horror with taboo subject matter.</t>
         </is>
       </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10403,6 +10942,11 @@
           <t>I don't have reliable information about a film called "Death Warrior" to provide an accurate summary of what viewer desires or needs it meets. There may be multiple films with similar titles, or this could be a lesser-known production. Without being able to verify specific details about this particular film, I cannot provide a meaningful analysis of its appeal to audiences.</t>
         </is>
       </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10491,6 +11035,11 @@
       <c r="X113" t="inlineStr">
         <is>
           <t>"Brothers" (2009) meets viewers' desires for emotionally intense drama exploring themes of war trauma, family loyalty, and moral complexity. It satisfies needs for psychological depth in examining PTSD's impact on soldiers and families, while providing compelling performances that explore jealousy, guilt, and the bonds between siblings. The film appeals to those seeking serious, character-driven stories about sacrifice and the hidden costs of military service.</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10576,6 +11125,11 @@
 - **Dramatic stakes** - High-tension scenarios with serious consequences
 - **Genre conventions** - Familiar erotic thriller or psychological thriller tropes that deliver expected pleasures
 The specific desires met depend on which version of "Dark Seduction" is being referenced, but most cater to audiences seeking suspenseful, adult-oriented dramatic entertainment with romantic/sexual elements.</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -10677,6 +11231,11 @@
 The film appeals to viewers wanting substantive genre entertainment that combines spectacle with ideas.</t>
         </is>
       </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10767,6 +11326,11 @@
           <t>"The Spy Next Door" meets viewers' desires for light family entertainment, combining action-comedy with wish-fulfillment fantasy. It appeals to children who enjoy spy adventures and physical comedy from Jackie Chan's signature stunts, while offering parents a safe, formulaic narrative about family bonding and acceptance. The film satisfies audiences seeking unchallenging escapism with predictable feel-good messages about stepfamily relationships and proving oneself worthy of love.</t>
         </is>
       </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10836,6 +11400,11 @@
         <is>
           <t># Summary
 *No Greater Love* meets viewers' desires for emotionally uplifting and faith-affirming content by presenting the Passion of Christ through a reverent, biblically faithful lens. It appeals to Christian audiences seeking spiritual enrichment, particularly during Lent and Holy Week, while offering educational value about Jesus's final hours. The film satisfies needs for accessible religious storytelling that inspires reflection on sacrifice, redemption, and divine love, providing both emotional catharsis and reinforcement of core Christian beliefs about salvation.</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10928,6 +11497,11 @@
 - **Fresh perspective** on a familiar character in a new setting away from Earth</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11026,6 +11600,11 @@
 7. **Dark psychological drama** - Appetite for disturbing, uncomfortable explorations of trauma and its consequences</t>
         </is>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11092,6 +11671,11 @@
           <t>"The Making of Daybreakers" meets viewer desires for behind-the-scenes insight into filmmaking, satisfying curiosity about special effects, vampire makeup, and production design. It appeals to fans of the original film who want deeper knowledge of how the dystopian vampire world was created, and to aspiring filmmakers interested in learning about independent film production techniques and creative problem-solving on a budget.</t>
         </is>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11183,6 +11767,11 @@
 The film "Killers" (2010) meets viewer desires for escapist entertainment through its blend of action-comedy romance. It satisfies the need for wish-fulfillment (an ordinary person discovering their partner leads a secret, exciting life), light humor, attractive stars (Ashton Kutcher and Katherine Heigl), explosive action sequences, and romantic fantasy. The film appeals to audiences seeking undemanding entertainment that combines relationship comedy with spy thriller elements, offering both couples-friendly content and adrenaline-pumping excitement without requiring deep emotional investment.</t>
         </is>
       </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11266,6 +11855,11 @@
 **Alpha and Omega** meets viewer desires for family-friendly entertainment with appealing animated animal characters, a lighthearted romantic storyline, and themes of friendship, teamwork, and overcoming social barriers. It satisfies children's enjoyment of colorful animation and humor while offering parents a safe, positive viewing experience with messages about acceptance and working together despite differences.</t>
         </is>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11358,6 +11952,11 @@
 - **Nostalgia**: Reunites iconic 1980s-90s action stars (Stallone, Statham, Li, Lundgren, Willis, Schwarzenegger), appealing to fans who grew up with these actors. - **Escapism and spectacle**: Delivers non-stop action, explosions, and combat sequences that provide pure entertainment without demanding emotional or intellectual engagement. - **Masculine power fantasy**: Features physically dominant heroes solving problems through strength and combat, appealing to traditional action genre expectations. - **Simple moral clarity**: Presents clear good vs. evil narratives where audiences can root for heroes without moral ambiguity. - **Camaraderie and loyalty**: Showcases bonds between warriors and themes of brotherhood that resonate with viewers valuing teamwork and loyalty. - **Vicarious thrills**: Offers safe experience of danger and violence through larger-than-life scenarios most viewers will never encounter.</t>
         </is>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11448,6 +12047,11 @@
           <t>"Burning Bright" meets viewers' desires for suspenseful thriller entertainment, combining survival horror with the primal fear of being trapped with a dangerous predator (a tiger). The film appeals to audiences seeking edge-of-your-seat tension, claustrophobic scenarios during a hurricane lockdown, and the satisfaction of watching characters use wit and determination to overcome seemingly impossible odds. It also taps into protective instincts through the protagonist's role as a sibling caring for her autistic brother while facing mortal danger.</t>
         </is>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11532,6 +12136,11 @@
       <c r="X125" t="inlineStr">
         <is>
           <t>"Beatdown" (2010) is an MMA/fighting film that appeals to viewers seeking intense combat action, underdog redemption stories, and gritty sports drama. It meets desires for physical competition spectacle, themes of personal transformation through martial arts, and the visceral excitement of underground fighting culture. The film caters to fans of mixed martial arts who enjoy watching fighters overcome personal struggles while delivering raw, brutal fight sequences.</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11632,6 +12241,11 @@
 The film primarily appeals to horror fans seeking intense sensory experiences and narrative payoff for franchise investment.</t>
         </is>
       </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11724,6 +12338,11 @@
 **Representation &amp; Validation**: The film addresses the experiences of Black women, providing much-needed representation and validation of their stories, struggles, and resilience that are often marginalized in mainstream media. **Emotional Catharsis**: It offers viewers an opportunity to process difficult topics like domestic violence, sexual assault, abortion, and abandonment through powerful storytelling and poetry. **Community &amp; Solidarity**: The film creates a sense of shared experience and sisterhood, helping viewers feel less alone in their struggles and fostering connection through collective trauma and healing. **Artistic Expression**: It satisfies the desire for poetic, lyrical storytelling that elevates difficult subject matter through beautiful language and performance, blending theater and cinema. **Social Awareness**: The film educates viewers about intersectional issues facing Black women and encourages conversations about gender, race, and systemic oppression. **Hope &amp; Healing**: Despite its heavy themes, the film ultimately offers messages of survival, strength, and the possibility of finding oneself and one's voice after</t>
         </is>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11814,6 +12433,11 @@
           <t># Summary: How *The Next Three Days* Meets Viewer Desires
 *The Next Three Days* satisfies several key viewer needs:
 **Escapist fantasy**: The film fulfills the desire to see an ordinary person successfully challenge an overwhelming system, offering vicarious thrills of outsmarting authority. **Emotional engagement**: It provides intense suspense and romantic devotion as a husband refuses to abandon his imprisoned wife, meeting needs for both tension and love-conquers-all sentiment. **Moral complexity**: The ambiguity about the wife's actual guilt engages viewers who appreciate ethical dilemmas over simple good-vs-evil narratives. **Underdog triumph**: Audiences experience satisfaction watching an average man transform into a capable action hero through determination and intelligence rather than superhuman abilities. **Justice fantasy**: For viewers frustrated with institutional failures, the film offers cathartic wish-fulfillment where personal action succeeds where the legal system failed.</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11916,6 +12540,11 @@
 The film appeals to audiences who enjoy smart, adult-oriented crime dramas with moral complexity.</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12000,6 +12629,11 @@
       <c r="X130" t="inlineStr">
         <is>
           <t>"Blood Out" appeals to viewers seeking an action-packed revenge thriller with martial arts combat, gang violence, and themes of family loyalty. It satisfies desires for straightforward vigilante justice narratives, intense fight sequences, and the visceral satisfaction of seeing a protagonist avenge a loved one through violent confrontation with criminal underworld figures.</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12097,6 +12731,11 @@
 - **Reflection on materialism and what truly matters**: The yard sale metaphor speaks to those questioning consumer culture and life priorities
 - **Will Ferrell in a dramatic role**: Fans curious to see the comedian demonstrate serious acting range
 The film satisfies the need for contemplative, melancholic storytelling that validates struggle while suggesting the possibility of renewal through acceptance and change.</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12189,6 +12828,11 @@
 - **Accessible superhero content** - Providing family-friendly entertainment for younger Marvel fans</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12277,6 +12921,11 @@
       <c r="X133" t="inlineStr">
         <is>
           <t>"Blitz" meets viewers' desires for historical drama and emotional storytelling by depicting London during World War II through the journey of a mother searching for her son amid the Blitz bombings. The film satisfies needs for compelling wartime narratives, themes of resilience and family bonds, visual spectacle of period recreation, and exploration of both personal and collective trauma during one of history's most significant conflicts.</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12378,6 +13027,11 @@
 The film appeals to audiences wanting challenging, socially conscious horror that prioritizes ideas and discomfort over traditional scares.</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12470,6 +13124,11 @@
 **Emotional catharsis** - The film delivers powerful family drama and reconciliation, allowing audiences to experience deep emotional release through the broken relationship between father and sons. **Underdog triumph** - Both brothers represent different types of underdogs fighting against overwhelming odds, fulfilling the desire to see determination rewarded. **Authentic action** - Intense, realistic MMA fight sequences provide visceral thrills and spectacle for action enthusiasts. **Moral complexity** - The film avoids simple heroes and villains, instead presenting flawed characters worthy of empathy, satisfying viewers who appreciate nuanced storytelling. **Redemption narrative** - Multiple characters seek second chances (the father's sobriety, the brothers' reconciliation), appealing to universal hopes for personal transformation and forgiveness. **Masculine emotional expression** - Provides a framework for exploring male vulnerability, pain, and connection through the socially acceptable vehicle of combat sports.</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12560,6 +13219,11 @@
           <t>"Abduction" meets viewer desires for fast-paced action and suspense, featuring a young protagonist discovering his true identity while evading dangerous pursuers. The film appeals to audiences seeking escapist entertainment with chase sequences, fight scenes, romantic tension, and a mystery-driven plot. It also capitalizes on the appeal of its young star, Taylor Lautner, targeting teen and young adult audiences looking for a thriller with relatable coming-of-age elements mixed with high-stakes adventure.</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12642,6 +13306,11 @@
           <t>"Fred 2: Night of the Living Fred" meets viewers' desires for lighthearted, family-friendly comedy and entertainment featuring the popular YouTube character Fred Figglehorn. The film appeals to young audiences and fans of the original Fred content who enjoy slapstick humor, exaggerated characters, and a simple Halloween-themed adventure story that doesn't require serious emotional investment.</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12732,6 +13401,11 @@
           <t># Summary of Viewer Desires/Needs Met by Black Rock
 **Black Rock** (2012) appeals to viewers seeking:
 - **Survival thriller tension** - The film delivers suspense through a life-or-death scenario where three women must outsmart and outfight dangerous men on an isolated island. - **Female empowerment narrative** - It provides a story where women transform from victims to fighters, taking agency and using strength and strategy to survive. - **Psychological drama** - The film explores fractured friendships and past conflicts being tested under extreme pressure. - **Revenge/justice satisfaction** - Viewers experience catharsis as the protagonists turn the tables on their attackers. - **Minimalist, raw filmmaking** - Appeals to audiences who appreciate stripped-down, realistic indie horror-thrillers without excessive special effects. - **Social commentary** - Addresses themes of male violence against women and toxic masculinity, resonating with viewers interested in feminist perspectives in genre films.</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12829,6 +13503,11 @@
 - **Moral affirmation**: Viewers see goodness rewarded and personal growth through helping others
 - **Aspirational lifestyle**: Displays wealth and success while suggesting money isn't everything
 - **Emotional catharsis**: The protagonist's journey from constrained corporate life to personal freedom resonates with desires for self-discovery and breaking free from societal expectations</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12930,6 +13609,11 @@
 The film satisfies both entertainment needs (action, drama, romance) and deeper psychological desires for justice, autonomy, and resistance against unfair systems.</t>
         </is>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13004,6 +13688,7 @@
           <t>"Adventures in Lalaloopsy Land: The Search for Pillow" meets young viewers' desires for colorful, gentle entertainment featuring friendship and teamwork. The film provides comfort through its predictable, low-stakes narrative, appealing visuals based on the popular doll franchise, and positive messages about helping others and working together. It satisfies children's need for familiar characters, simple problem-solving adventures, and reassuring stories where friends overcome challenges through cooperation.</t>
         </is>
       </c>
+      <c r="Y141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13094,6 +13779,11 @@
           <t>"Safe" meets viewers' desires for psychological horror that explores environmental illness, social alienation, and modern anxieties about contamination and control. It appeals to those seeking ambiguous, art-house cinema that critiques consumerism, wellness culture, and the vulnerability of middle-class existence without providing easy answers or conventional narrative resolution.</t>
         </is>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13185,6 +13875,11 @@
 "What to Expect When You're Expecting" meets viewer desires for relatable content about pregnancy and parenthood, offering validation of the diverse experiences—both joyful and challenging—that come with expecting a baby. The ensemble cast appeals to audiences seeking lighthearted entertainment with emotional resonance, while the film provides comfort through shared struggles with fertility, adoption, body changes, and relationship dynamics. It satisfies the need for representation of different family-building journeys and offers humor as a coping mechanism for an often stressful life transition.</t>
         </is>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13269,6 +13964,11 @@
       <c r="X144" t="inlineStr">
         <is>
           <t>"Mighty Fine" meets viewers' desires for family drama that explores the complexities of maintaining appearances while dealing with personal struggles. The film appeals to audiences interested in stories about family dysfunction, the dark side of the American Dream, and the impact of a charismatic but troubled patriarch on his wife and daughters. It satisfies viewers seeking emotionally intense narratives about economic hardship, domestic tension, and the resilience of family bonds during crisis.</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13370,6 +14070,11 @@
 The film provides feel-good entertainment that combines impressive choreography with accessible themes of resistance, creativity, and following your dreams.</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13460,6 +14165,11 @@
           <t># The Expendables 2: Viewer Desires Met
 **The Expendables 2** satisfies several key audience desires:
 **Nostalgia** - Features 1980s-90s action stars (Stallone, Schwarzenegger, Willis, Van Damme, Norris) reunited on screen, appealing to fans who grew up with these icons. **Escapism and spectacle** - Delivers explosive, over-the-top action sequences, stunts, and violence that provide pure entertainment without complex plots. **Male camaraderie fantasy** - Showcases brotherhood, loyalty, and teamwork among tough warriors, fulfilling desires for masculine bonding and honor codes. **Simple good vs. evil narrative** - Offers clear-cut heroes and villains with straightforward morality, providing satisfaction through predictable justice. **Power fantasy** - Allows viewers to vicariously experience physical dominance, combat skills, and invincibility through superhuman characters. **Self-aware humor** - Includes meta-jokes and references that reward longtime action fans while acknowledging the film's intentional camp value. The film essentially serves as comfort food for</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13559,6 +14269,11 @@
 The film provides escapist entertainment while tapping into universal anxieties about family dissolution, children in danger, and malevolent forces threatening domestic safety.</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13650,6 +14365,11 @@
 *The Bay* (2012) meets viewer desires for eco-horror thrills and found-footage suspense. It satisfies audiences seeking cautionary environmental tales about pollution and government cover-ups, while delivering body horror through parasitic infection. The film appeals to fans of disaster movies and mockumentary-style storytelling, offering visceral scares and social commentary about ecological negligence and its consequences.</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13736,6 +14456,11 @@
           <t>I don't have any information about "The Yummy Gummy Search for Santa" in my knowledge base, so I cannot provide details about what viewer desires or needs this film meets.</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13808,6 +14533,11 @@
 The compilation format satisfies the desire for multiple short stories that match young children's limited attention spans while reinforcing positive social values.</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13898,6 +14628,11 @@
           <t>"Stand Up Guys" meets viewer desires for nostalgic entertainment featuring beloved veteran actors (Al Pacino, Christopher Walken, Alan Arkin), blending crime drama with dark comedy and themes of friendship, loyalty, and aging. It appeals to audiences seeking a character-driven story about older protagonists confronting mortality while maintaining their dignity and bond, offering both action and emotional depth with bittersweet humor about growing old but staying true to one's code.</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13974,6 +14709,11 @@
       <c r="X152" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "Aztec Warrior" in my knowledge base. Without knowing the particular film you're referring to (as there may be multiple films with similar titles), I cannot accurately describe what viewer desires or needs it meets. If you could provide additional details like the release year or director, I might be able to help better.</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14074,6 +14814,11 @@
 The film primarily serves fans seeking familiar franchise elements with updated technical presentation.</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14171,6 +14916,11 @@
 - **Justice and moral clarity** - The film delivers a satisfying resolution where good prevails and the hero protects his community</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14237,6 +14987,7 @@
           <t>"Lalaloopsy: A Sew Magical Tale" meets young children's desires for colorful, whimsical entertainment featuring friendship, creativity, and problem-solving. The film appeals to fans of the Lalaloopsy doll franchise while providing gentle life lessons about teamwork, imagination, and helping others. It offers parents a safe, age-appropriate viewing option that promotes positive values and social skills for preschool and early elementary-aged viewers.</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14335,6 +15086,11 @@
 The film primarily appeals to audiences seeking entertainment that reinforces traditional values through dramatic negative examples.</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14430,6 +15186,11 @@
 4. **Cautionary insight** - meets the need for understanding digital-age dangers and their consequences
 5. **Human connection** - despite its title, ultimately affirms the importance of authentic relationships, satisfying viewers' desire for meaningful resolution
 The film serves as both a mirror to modern digital life and a warning about maintaining genuine human connection in an increasingly virtual world.</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14531,6 +15292,11 @@
 The film appeals to action fans wanting substance and drama audiences interested in gritty, urban character studies.</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14609,6 +15375,7 @@
           <t>I don't have reliable information about a film called "American Idiots." There may be confusion with the Green Day album "American Idiot" (2004) or its Broadway musical adaptation, but I cannot provide accurate information about viewer desires met by a specific film with that title without risking misinformation.</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14707,6 +15474,11 @@
 The film meets the desire for psychological suspense grounded in reality, with moral resolution through the capture of a dangerous criminal.</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14797,6 +15569,11 @@
           <t># Viewer Desires and Needs Met by "All Is Lost"
 **All Is Lost** satisfies several key viewer desires:
 **Survival and resilience**: The film taps into the primal human fascination with survival against overwhelming odds, allowing viewers to experience extreme perseverance vicariously. **Minimalist storytelling**: It meets the desire for pure, visual cinema stripped of dialogue and exposition, appealing to audiences seeking an immersive, meditative experience. **Existential contemplation**: The film provides space for reflection on mortality, isolation, and human determination, satisfying viewers drawn to philosophical or introspective narratives. **Technical admiration**: It fulfills appreciation for masterful filmmaking craft, including Robert Redford's nearly wordless performance and the realistic portrayal of maritime challenges. **Emotional catharsis**: The intense struggle offers emotional release through tension, despair, and ultimate hope, meeting the need for a profound emotional journey.</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14897,6 +15674,11 @@
 The film targets viewers who enjoy trashy, sensationalized entertainment that prioritizes spectacle over substance.</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14965,6 +15747,11 @@
       <c r="X163" t="inlineStr">
         <is>
           <t>"Alpha and Omega 2: A Howl-iday Adventure" meets viewer desires for family-friendly entertainment, particularly appealing to young children. It provides lighthearted humor, cute animal characters, holiday themes that create seasonal warmth, simple moral lessons about family and friendship, and non-threatening conflict resolution. The film serves as accessible, safe content for parents seeking harmless entertainment to occupy children, with familiar characters from the franchise offering continuity for fans of the original movie.</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15065,6 +15852,11 @@
 - **Justice and revenge** - Emotional payoff of seeing wronged characters prevail against corrupt authority</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15155,6 +15947,11 @@
           <t># Viewer Desires and Needs Met by The Hunger Games: Catching Fire
 **The Hunger Games: Catching Fire** satisfies several key viewer desires:
 **Escapism and spectacle** - The film provides visually stunning dystopian world-building, elaborate costumes, and intense action sequences that transport audiences from everyday life. **Empowerment and resistance** - Viewers experience vicarious satisfaction through Katniss's defiance against oppressive authority, appealing to desires for justice and standing up to tyranny. **Romantic tension** - The love triangle between Katniss, Peeta, and Gale fulfills desires for emotional drama and relationship intrigue. **Survival and competition** - The life-or-death arena setting taps into primal interests in watching skilled individuals overcome deadly challenges. **Social commentary** - The film addresses real-world concerns about inequality, media manipulation, and authoritarian control, satisfying viewers' need for meaningful content. **Identification with a strong protagonist** - Katniss serves as an aspirational figure, particularly for young women seeking capable, complex heroes. **Community and solidarity** - The alliance-building</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15256,6 +16053,11 @@
 The film appeals to audiences interested in war dramas, true stories, and character-driven narratives about resilience and redemption.</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15323,6 +16125,11 @@
           <t>"Bob the Builder: Animal Adventures" meets young children's desires for entertainment featuring friendly characters, simple problem-solving stories, and positive messages about teamwork and helping others. The animal theme appeals to kids' natural interest in creatures while providing educational content about construction, cooperation, and caring for animals in an accessible, non-threatening format that parents trust for preschool-aged viewers.</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15413,6 +16220,11 @@
           <t>"A Madea Christmas" meets viewers' desires for lighthearted holiday entertainment, family-oriented comedy, and feel-good messages about forgiveness, community unity, and Christmas spirit. The film appeals to fans of Tyler Perry's Madea character who enjoy physical comedy and cultural humor, while also providing themes of overcoming prejudice and celebrating togetherness that resonate during the holiday season.</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15487,6 +16299,11 @@
           <t># Summary
 *The Gospel of Matthew* (1964) meets viewers' desires for:
 **Spiritual/Religious fulfillment** - Provides a faithful, reverent presentation of Scripture for believers seeking connection with Christ's life and teachings. **Artistic/Aesthetic appreciation** - Offers stark, beautiful black-and-white cinematography and neorealist style that appeals to cinephiles. **Educational value** - Serves as an accessible visual introduction to biblical narrative for those seeking to understand Christian foundations. **Emotional resonance** - Delivers moments of compassion, suffering, and transcendence that satisfy needs for meaningful, contemplative cinema. **Authenticity** - Uses direct biblical text and non-professional actors to create an unadorned, historically grounded experience that counters Hollywood spectacle.</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15588,6 +16405,11 @@
 The film essentially serves viewers wanting a straightforward supernatural action movie with recognizable IP and blockbuster-style presentation.</t>
         </is>
       </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15674,6 +16496,7 @@
 The film primarily serves parents seeking educational entertainment that reinforces prosocial values for children ages 2-6.</t>
         </is>
       </c>
+      <c r="Y171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15766,6 +16589,11 @@
 **Representation and Validation**: Single mothers see their struggles, challenges, and triumphs reflected on screen, providing a sense of being seen and understood. **Community and Connection**: The film fulfills the need for stories about friendship, support networks, and women helping each other through difficult times. **Escapism with Relatability**: Offers lighthearted entertainment while addressing real issues like financial stress, dating as a parent, and work-life balance. **Empowerment**: Provides uplifting messages about female strength, resilience, and the ability to overcome obstacles. **Romance and Hope**: Includes romantic subplots that offer wish fulfillment and optimism about finding love while raising children alone. **Comedy Relief**: Delivers humor and feel-good moments that provide stress relief for audiences dealing with similar real-life pressures.</t>
         </is>
       </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15842,6 +16670,7 @@
 **Young children (ages 4-8)** seeking familiar characters and simple entertainment. The film provides colorful animation, anthropomorphic animal characters, slapstick humor, and straightforward storylines about friendship and teamwork. **Parents** looking for inexpensive, readily available home entertainment that keeps young children occupied with G-rated content featuring positive messages about family values, cooperation, and perseverance. **Fans of the franchise** who desire continuation of the Alpha and Omega series, offering comfort through recognizable characters and predictable story structures. The film serves as accessible, undemanding viewing that requires minimal parental supervision while delivering conventional moral lessons in an animated animal adventure format.</t>
         </is>
       </c>
+      <c r="Y173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15937,6 +16766,11 @@
 4. **Insider expertise** - Appeals to sports fans who want to feel knowledgeable about draft strategy, trades, and team-building
 5. **Wish fulfillment** - Lets viewers fantasize about being the mastermind making crucial decisions that affect a beloved sports franchise
 6. **Emotional stakes** - Balances professional drama with personal conflict (family, relationships) for broader appeal beyond just sports fans</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -16038,6 +16872,11 @@
 The film appeals to audiences interested in dark, character-driven indie dramas that don't offer easy answers or conventional heroism.</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16127,6 +16966,11 @@
 The film appeals to audiences seeking thoughtful LGBTQ+ narratives set against high-stakes professional and moral conflicts.</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16213,6 +17057,11 @@
           <t>"They Came Together" meets viewer desires for comedy that satirizes romantic comedy clichés and conventions. It appeals to audiences who enjoy self-aware, meta-humor and parody films that mock the predictable tropes of the rom-com genre while simultaneously delivering laughs through absurdist comedy and over-the-top performances from its cast, including Paul Rudd and Amy Poehler.</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16281,6 +17130,11 @@
 **Family Entertainment**: Provides safe, child-appropriate content parents can watch with young children without concern. **Adventure and Excitement**: Delivers action-packed sequences and suspenseful moments that keep young audiences engaged. **Familiar Characters**: Continues a franchise with established characters that existing fans want to see more of. **Humor**: Offers lighthearted comedy and slapstick moments aimed at entertaining children. **Positive Messages**: Reinforces themes of teamwork, courage, family bonds, and problem-solving that parents appreciate. **Accessible Viewing**: Serves as easy, undemanding entertainment requiring minimal attention or emotional investment—ideal for casual family movie time or keeping children occupied.</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16369,6 +17223,11 @@
       <c r="X179" t="inlineStr">
         <is>
           <t>"My Man Is a Loser" is a romantic comedy that appeals to viewers seeking light entertainment about relationship struggles and male friendship. It meets the desire for wish-fulfillment scenarios where struggling husbands learn to rekindle romance with their wives, offers comedic relief through awkward situations, and provides reassurance that marital problems can be overcome with effort and outside help. The film caters to audiences looking for accessible, low-stakes comedy about relatable relationship dynamics without requiring deep emotional investment.</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -16471,6 +17330,11 @@
 The film appeals to audiences who prefer thought-provoking dramas over conventional thrillers.</t>
         </is>
       </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16571,6 +17435,11 @@
 The film primarily serves viewers wanting unchallenging, testosterone-driven action entertainment with nostalgic appeal.</t>
         </is>
       </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16669,6 +17538,11 @@
 The film serves audiences looking for visceral, no-frills monster horror rather than the campy tone of earlier Leprechaun films.</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16739,6 +17613,11 @@
 The film appeals to fans of le Carré's work, espionage history enthusiasts, and those interested in the creative process of acclaimed writers.</t>
         </is>
       </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16832,6 +17711,11 @@
 The film satisfies those wanting a comedy that doesn't shy away from real issues like divorce, aging, and death, while ultimately affirming family connections and life's joyful moments.</t>
         </is>
       </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16929,6 +17813,11 @@
 The film appeals to fans of campy horror who enjoy self-aware genre exercises that blend scares with comedic absurdity.</t>
         </is>
       </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17019,6 +17908,11 @@
           <t>The film "Addicted" (2014) meets viewer desires for erotic thriller entertainment, exploring themes of sexual addiction, forbidden desire, and marital infidelity. It appeals to audiences seeking steamy romance, relationship drama, and the psychological tension of a successful woman risking everything for passion. The film caters to those interested in provocative storylines about female sexuality and the consequences of obsessive behavior.</t>
         </is>
       </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17109,6 +18003,11 @@
           <t>"Dear White People" meets viewers' desires for sharp social commentary on race relations, representation of Black college experiences, and intelligent satire that challenges both liberal and conservative perspectives on identity politics. It provides catharsis for audiences frustrated with racial microaggressions and offers educational value through its witty examination of systemic racism, cultural appropriation, and the complexities of navigating predominantly white institutions. The film also satisfies those seeking diverse storytelling that balances humor with serious cultural critique.</t>
         </is>
       </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17199,6 +18098,11 @@
           <t>"See No Evil 2" meets viewer desires for slasher horror thrills, featuring gore, suspense, and a hulking supernatural killer stalking victims in a claustrophobic morgue setting. It appeals to fans seeking visceral scares, creative death scenes, and the guilty pleasure of a straightforward survival horror film with minimal plot complexity.</t>
         </is>
       </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17289,6 +18193,11 @@
           <t>"Jessabelle" meets viewers' desires for supernatural horror thrills, including ghost story scares, Southern Gothic atmosphere, mystery-solving suspense, and themes of uncovering dark family secrets. The film appeals to audiences seeking jump scares, occult elements involving voodoo and tarot cards, and a twist ending that recontextualizes the entire narrative.</t>
         </is>
       </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17381,6 +18290,11 @@
 **Escapism and spectacle** - The dystopian world offers an immersive break from reality with striking visuals and production design. **Emotional catharsis** - The film provides outlets for processing feelings about oppression, trauma, and resistance through Katniss's journey. **Empowerment fantasy** - Viewers experience vicarious strength through watching ordinary people challenge authoritarian power structures. **Social commentary** - It fulfills the desire to engage with relevant themes like propaganda, media manipulation, and political resistance. **Character investment** - Continuation of beloved characters' arcs satisfies fans' emotional connection to the ongoing story. **Moral clarity** - The clear good vs. evil conflict provides satisfying narrative structure in an uncertain world. **Community and belonging** - Shared cultural experience with other fans creates social connection and collective meaning-making.</t>
         </is>
       </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17467,6 +18381,11 @@
           <t>"Dying of the Light" (2014) appeals to viewers seeking a thriller about a CIA agent racing against time while battling dementia, offering Nicolas Cage fans action and suspense, those interested in espionage stories, audiences drawn to themes of personal decline and professional redemption, and viewers who appreciate revenge narratives where an aging protagonist pursues a terrorist nemesis from his past.</t>
         </is>
       </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17555,6 +18474,11 @@
       <c r="X192" t="inlineStr">
         <is>
           <t>"Wild Card" meets viewer desires for action-packed entertainment through Jason Statham's signature fight sequences and tough-guy persona. The film appeals to those seeking a straightforward revenge thriller with casino-set Las Vegas glamour, gambling tension, and stylized violence. It satisfies audiences looking for a lean, no-nonsense action vehicle featuring a morally ambiguous protagonist navigating the criminal underworld, combining elements of neo-noir atmosphere with visceral hand-to-hand combat scenes.</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -17650,6 +18574,11 @@
 The film appeals to audiences who enjoy heartwarming, socially conscious stories about perseverance, mentorship, and achieving success against the odds.</t>
         </is>
       </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17738,6 +18667,11 @@
       <c r="X194" t="inlineStr">
         <is>
           <t>"Mortdecai" appeals to viewers seeking light escapist entertainment through its combination of art-world heist comedy, slapstick humor, and eccentric characters. It satisfies desires for visually stylish period aesthetics, Johnny Depp's quirky comedic performance, and a breezy caper plot that doesn't require serious intellectual engagement—offering mindless fun and glamorous international settings for those wanting undemanding entertainment.</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -17836,6 +18770,11 @@
 - **Familiar faces** - Stars Olivia Wilde and Mark Duplass for recognizable appeal
 - **Tension and suspense** - Escalating paranormal danger and survival stakes
 - **Cautionary tale satisfaction** - The fulfillment of seeing hubris punished in classic horror tradition</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -17938,6 +18877,11 @@
 The film satisfies audiences interested in dark historical thrillers that combine crime investigation with political oppression.</t>
         </is>
       </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -18031,6 +18975,11 @@
 **Visual spectacle** - Delivers production design and battle sequences for those seeking cinematic scope</t>
         </is>
       </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -18128,6 +19077,11 @@
 - **Emotional catharsis**: The tension between self-preservation and vulnerability in love, resolved through sacrifice and redemption</t>
         </is>
       </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18221,6 +19175,11 @@
 3. **Exploration of grief and loss** - Addresses the emotional process of watching a loved one deteriorate from terminal illness (metaphorically through zombie infection)
 4. **Slow-burn, atmospheric storytelling** - Appeals to audiences seeking contemplative, art-house approach to genre filmmaking
 5. **Father-daughter relationship focus** - Centers on familial love and the lengths parents go to protect their children</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -18305,6 +19264,11 @@
 The film essentially serves viewers interested in health conspiracies, anti-corporate sentiment, and food industry skepticism.</t>
         </is>
       </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18383,6 +19347,11 @@
           <t>"Twilight Storytellers: The Mary Alice Brandon File" meets viewer desires for deeper backstory and origin stories of beloved characters from the Twilight universe. It satisfies fans' curiosity about Alice Cullen's mysterious human past, including her time in an asylum and transformation into a vampire—details only briefly mentioned in the main series. The film appeals to those seeking darker, more mature content within the Twilight world, exploring themes of mental illness, medical mistreatment, and identity that go beyond the main saga's romantic focus.</t>
         </is>
       </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18453,6 +19422,11 @@
           <t>"Twilight Storytellers: We've Met Before" is a fan-made short film that meets viewers' desires for expanded Twilight universe content, exploring the backstory of minor characters Garrett and Kate. It satisfies fans' interests in romantic relationships within the vampire world, provides deeper lore about the Denali coven, and offers additional content beyond the main saga while maintaining the franchise's signature themes of eternal love and supernatural romance.</t>
         </is>
       </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18544,6 +19518,11 @@
 **The Vatican Tapes** meets viewer desires for supernatural horror and religious terror. It appeals to audiences seeking demonic possession scares, found-footage style tension, exorcism drama, and Catholic Church mythology. The film satisfies those who enjoy jump scares, apocalyptic stakes, and the familiar tropes of spiritual warfare between good and evil, offering a visceral thrill experience within the paranormal horror genre.</t>
         </is>
       </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18622,6 +19601,11 @@
           <t>"Alpha and Omega: Family Vacation" meets viewers' desires for light family entertainment, particularly targeting young children with its simple storyline about wolf pups on an adventure. The film appeals to parents seeking non-violent, easy-to-follow content for kids, while offering themes of family bonding and working together. It satisfies the need for inexpensive, accessible animated content that can occupy children's attention without requiring parental concern about inappropriate material.</t>
         </is>
       </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18710,6 +19694,11 @@
       <c r="X205" t="inlineStr">
         <is>
           <t>"Brothers" meets viewers' desires for intense emotional drama, exploring themes of family loyalty, the psychological impact of war and PTSD, moral complexity in extreme situations, and the strain trauma places on relationships. It appeals to those seeking serious, character-driven stories about sacrifice, guilt, and the challenges of homecoming for veterans.</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -18811,6 +19800,11 @@
 The film combines genre pleasures—comedy, action, romance, and thriller—to create light, disposable entertainment for audiences wanting an unconventional action movie with humor and heart.</t>
         </is>
       </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18901,6 +19895,11 @@
           <t>"Chain of Command" (1994) meets viewer desires for action-packed military entertainment, featuring combat sequences, espionage thrills, and a straightforward good-vs-evil narrative. The film appeals to audiences seeking escapist entertainment with a heroic protagonist fighting against terrorists, satisfying needs for patriotic themes, physical spectacle, and clear moral resolution typical of 1990s direct-to-video action films.</t>
         </is>
       </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18995,6 +19994,11 @@
 - **Justice and revenge satisfaction**: Offers catharsis through a hero exposing corruption and fighting back
 - **Suspenseful pacing**: Creates tension through time pressure and confined setting challenges
 - **Accessible viewing**: Requires no prior knowledge of the franchise; offers uncomplicated, visceral entertainment</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -19067,6 +20071,7 @@
 The film provides reassurance and gentle life lessons in a colorful, non-threatening format designed for preschool audiences.</t>
         </is>
       </c>
+      <c r="Y209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -19166,6 +20171,11 @@
 The film appeals to viewers who appreciate sophisticated, thought-provoking thrillers that challenge comfortable notions of right and wrong.</t>
         </is>
       </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19256,6 +20266,11 @@
           <t>The film *Stonewall* (2015) aims to meet viewers' desires for historical drama about LGBTQ+ rights by depicting the 1969 Stonewall riots, a pivotal moment in the gay liberation movement. It appeals to audiences seeking inspirational narratives about marginalized communities fighting for equality, coming-of-age stories within queer contexts, and representation of LGBTQ+ history on screen. However, the film was controversial for centering a fictional white cisgender protagonist rather than the transgender women and people of color who were central to the actual events, limiting its effectiveness in meeting the need for authentic historical representation.</t>
         </is>
       </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -19324,6 +20339,11 @@
 **Behind-the-scenes insight** - Fans of *Turbo Kid* get an in-depth look at how the cult film was created, satisfying curiosity about practical effects, production challenges, and creative decisions. **Nostalgia and genre appreciation** - Appeals to enthusiasts of 1980s-inspired action, DIY filmmaking, and retro-futuristic aesthetics who want to understand the film's homage to that era. **Filmmaking education** - Aspiring filmmakers and cinephiles learn about low-budget independent production techniques, special effects creation, and the passion required to bring unconventional visions to life. **Community connection** - Provides fans a deeper connection to the filmmakers and cast, fostering appreciation for the dedication behind cult cinema.</t>
         </is>
       </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -19396,6 +20416,11 @@
       <c r="X213" t="inlineStr">
         <is>
           <t>"Game Changer: The Legacy of Saw" is a documentary that meets viewers' desires for behind-the-scenes insight into the making of the influential "Saw" horror franchise. It appeals to fans seeking to understand the creative process, the franchise's cultural impact on horror cinema, and nostalgic appreciation for how the low-budget original film revolutionized the torture-horror subgenre. The documentary satisfies curiosity about the filmmakers' journey and the series' lasting influence on modern horror.</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -19497,6 +20522,11 @@
 The film serves as accessible, low-commitment entertainment for action-fantasy fans wanting a popcorn movie experience.</t>
         </is>
       </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19593,6 +20623,11 @@
 5. **Romance Resolution** - Concludes the love triangle between Katniss, Peeta, and Gale
 6. **Justice and Empowerment** - Depicts the overthrow of tyranny and shows a young woman as a powerful agent of change, appealing to desires for fairness and representation
 7. **Escapism** - Provides immersion in a dyst</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -19686,6 +20721,11 @@
 The film primarily targets parents looking for G-rated content to occupy young children, rather than audiences seeking sophisticated storytelling or animation quality.</t>
         </is>
       </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -19774,6 +20814,11 @@
       <c r="X217" t="inlineStr">
         <is>
           <t>"Dirty Grandpa" appeals to viewers seeking raunchy, irreverent comedy and escapist entertainment. It satisfies desires for shock humor, transgressive behavior, and watching established actors like Robert De Niro play against type in outrageous scenarios. The film caters to audiences wanting mindless fun, sexual humor, and a break from more serious or demanding cinema, while also offering a formulaic story about breaking free from social constraints and embracing spontaneity.</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -19874,6 +20919,11 @@
 The film attempts to satisfy multiple audience segments simultaneously, though its fragmented narrative style may only partially fulfill these desires for most viewers.</t>
         </is>
       </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19972,6 +21022,11 @@
 The film provides a cathartic experience for viewers who enjoy tearjerker romances with uplifting resolutions.</t>
         </is>
       </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -20070,6 +21125,11 @@
 The film primarily serves audiences looking for light, visually-driven fantasy adventure rather than sophisticated storytelling or cultural authenticity.</t>
         </is>
       </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -20160,6 +21220,11 @@
           <t>"Allegiant" appeals to viewers seeking young adult dystopian action and adventure, providing closure to fans invested in the Divergent series and its characters. The film satisfies desires for romantic subplots, visual spectacle with futuristic technology and settings, and themes of rebellion against oppressive systems.</t>
         </is>
       </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -20250,6 +21315,11 @@
           <t>"The Perfect Match" meets viewers' desires for romantic escapism, wish fulfillment through an attractive cast and glamorous lifestyle, light entertainment without demanding deep thought, and the comforting formula of a romantic comedy where initial player/commitment-phobe characters eventually find true love. It provides easy-watching entertainment with aspirational romance and humor.</t>
         </is>
       </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -20326,6 +21396,11 @@
       <c r="X223" t="inlineStr">
         <is>
           <t>Natural Born Pranksters meets viewers' desires for shock value, outrageous humor, and vicarious thrills through elaborate practical jokes and stunts. It appeals to fans of YouTube prank culture who seek edgy, boundary-pushing comedy and the adrenaline of watching others be surprised or embarrassed in public settings. The film also satisfies curiosity about internet celebrities and offers escapist entertainment through over-the-top scenarios that viewers wouldn't experience in everyday life.</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -20427,6 +21502,11 @@
 The film appeals to audiences wanting a fast-paced, brain-meets-brawn thriller with redemption themes.</t>
         </is>
       </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -20519,6 +21599,11 @@
 **Escapism and exotic setting** - The Saudi Arabian desert landscape provides visual novelty and cultural immersion. **Relatable midlife crisis narrative** - Tom Hanks' struggling salesman resonates with audiences facing economic anxiety, career disappointment, and questions of relevance. **Gentle comedy-drama balance** - Offers light humor without demanding intensity, appealing to those wanting accessible entertainment. **Themes of reinvention and hope** - Meets the need for optimistic storytelling about second chances and personal transformation. **Cultural curiosity** - Provides a Western perspective on Middle Eastern business culture and daily life. **Tom Hanks' star appeal** - His everyman likability satisfies fans seeking his characteristic warmth and authenticity. The film serves viewers wanting thoughtful but undemanding drama about finding purpose and connection in unfamiliar circumstances.</t>
         </is>
       </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -20595,6 +21680,11 @@
       <c r="X226" t="inlineStr">
         <is>
           <t>"Alpha and Omega: Dino Digs" meets viewer desires for family-friendly entertainment, featuring talking animals, adventure, and humor aimed at young children. It provides lighthearted escapism with simple storylines about friendship and teamwork, appealing to kids who enjoy animated animal characters and dinosaur-related themes. The film offers parents an inexpensive, accessible viewing option to keep children entertained with non-threatening content.</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -20696,6 +21786,11 @@
 The film appeals to those seeking clever, light-hearted thriller entertainment that rewards attention while providing popcorn-movie fun.</t>
         </is>
       </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20794,6 +21889,11 @@
 - **Cautionary satisfaction** - seeing consequences of reckless online behavior while being entertained</t>
         </is>
       </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -20884,6 +21984,11 @@
           <t>"Skiptrace" meets viewers' desires for lighthearted action-comedy entertainment through its buddy-cop formula pairing Jackie Chan and Johnny Knoxville. The film delivers familiar Chan-style martial arts sequences, physical comedy, fish-out-of-water humor from cultural clashes, and a formulaic but feel-good adventure across China. It appeals to audiences seeking undemanding escapist entertainment with charismatic stars, exotic locations, and a mix of action and laughs without requiring deep emotional or intellectual investment.</t>
         </is>
       </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20977,6 +22082,11 @@
 3. **Neo-Western aesthetic** - Delivers the satisfaction of classic Western archetypes (outlaws, lawmen, frontier justice) updated for modern America. 4. **Brotherhood and loyalty** - Fulfills emotional needs through the strong sibling bond and sacrificial love between the brothers. 5. **Intelligent crime thriller** - Provides tension and suspense through a well-crafted heist narrative with strategic planning rather than mindless action. 6. **Authentic sense of place** - Offers cultural exploration of a rarely-depicted part of America (West Texas), satisfying curiosity about regional identity and working-class struggles. The film essentially meets desires</t>
         </is>
       </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -21067,6 +22177,11 @@
           <t>"Blood Father" meets viewers' desires for intense action, redemption narratives, and gritty crime thrillers. It appeals to those seeking a straightforward revenge story with visceral violence, a hardened anti-hero protecting his daughter, and Mel Gibson's return to a familiar tough-guy role. The film satisfies audiences who enjoy B-movie aesthetics, fast-paced plotting, and themes of parental sacrifice and second chances within an uncompromising, brutal underworld setting.</t>
         </is>
       </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -21151,6 +22266,11 @@
       <c r="X232" t="inlineStr">
         <is>
           <t>"Brotherhood" (depending on which film you're referring to) typically meets viewers' desires for intense drama, exploration of loyalty and family bonds, moral complexity, and gritty realism. The film often appeals to those seeking stories about sacrifice, the consequences of violence, brotherhood/camaraderie under pressure, and characters facing difficult ethical choices. It satisfies needs for emotionally powerful storytelling and examination of masculinity, duty, and the bonds that both unite and complicate relationships between men in extreme circumstances.</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21247,6 +22367,11 @@
 The film primarily serves audiences seeking accessible, culturally-specific comedy rather than challenging or innovative cinema.</t>
         </is>
       </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -21339,6 +22464,11 @@
 **Fear and Thrill-Seeking**: Delivers genuine scares and suspense through psychological horror rather than gore, satisfying audiences craving authentic terror. **Immersive Realism**: The found-footage style creates a documentary-like authenticity that makes viewers feel like witnesses to real events, enhancing engagement. **Mystery and the Unknown**: Taps into fascination with the supernatural, folklore, and unsolved mysteries, leaving much to imagination. **Vicarious Experience**: Allows safe exploration of dangerous, frightening situations from the comfort of a theater seat. **Cultural Participation**: Became a phenomenon that viewers wanted to experience and discuss as part of a shared cultural moment. **Low-Budget Authenticity**: Offered an alternative to polished Hollywood horror, appealing to audiences seeking raw, unfiltered storytelling. The film essentially satisfies the desire for innovative, psychologically disturbing horror that feels uncomfortably real.</t>
         </is>
       </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -21417,6 +22547,11 @@
           <t>"Elephant Kingdom" meets viewers' desires for family-friendly adventure entertainment, combining wildlife documentary elements with a narrative story. It appeals to those interested in elephant conservation, African landscapes, and heartwarming animal stories. The film satisfies needs for educational content about wildlife while providing an accessible, feel-good viewing experience suitable for children and adults who enjoy nature-themed films with environmental messages.</t>
         </is>
       </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -21503,6 +22638,11 @@
           <t>"End of a Gun" meets viewer desires for straightforward action entertainment, featuring gunfights, car chases, and physical confrontations. It appeals to fans of Steven Seagal's signature tough-guy persona and delivers a simple revenge/vigilante narrative with minimal complexity. The film satisfies those seeking undemanding, B-movie action with a recognizable star, providing escapist violence and a clear good-versus-evil storyline without requiring emotional investment or deep thought.</t>
         </is>
       </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -21593,6 +22733,11 @@
           <t>"Dirty 30" meets viewer desires for lighthearted escapism and female friendship celebration. The comedy appeals to audiences seeking relatable stories about turning 30, navigating life transitions, and maintaining close friendships through wild adventures. It satisfies needs for female-centered humor, nostalgia for carefree partying, and feel-good entertainment that doesn't require deep emotional investment—offering a fun, breezy watch for those wanting to laugh at the chaos of adulting while celebrating female bonds.</t>
         </is>
       </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -21685,6 +22830,11 @@
 **Spectacle and Action** - The film delivers intense disaster sequences and visual effects showing the catastrophic oil rig explosion, appealing to audiences seeking thrilling, large-scale action. **Real-life Drama** - Based on the 2010 BP oil spill disaster, it meets the desire for true stories and documentary-style realism about significant historical events. **Heroism and Survival** - The film showcases ordinary workers becoming heroes under extreme circumstances, fulfilling the need for inspirational stories of human courage and resilience. **Emotional Catharsis** - Through depicting tragedy and loss, it provides an outlet for processing collective grief about the disaster and its victims. **Social Awareness** - The film addresses corporate negligence and environmental catastrophe, satisfying viewers interested in social justice and accountability themes. **Technical Appreciation** - For some audiences, it offers insight into the complex operations of offshore drilling and industrial work environments.</t>
         </is>
       </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -21759,6 +22909,11 @@
 - **Chinese fantasy genre fans**: Delivers a wuxia-influenced story adapted from popular Chinese author Guo Jingming's work
 - **Action and spectacle**: Provides large-scale magical combat sequences and dramatic confrontations between powerful warriors
 The film primarily satisfies desires for eye candy, fantastical escapism, and melodramatic storytelling in a heavily stylized visual package.</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -21856,6 +23011,11 @@
 - **Humor and escapism** - providing comedy through the protagonist's pranks and animated fantasy sequences
 - **Emotional connection** - addressing deeper themes like grief, family dynamics, and self-acceptance that resonate with both kids and parents
 - **Validation** - reassuring young viewers that feeling like an outsider is normal and that challenging unfair systems is worthwhile</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21957,6 +23117,11 @@
 The film balances brutal realism with inspiring idealism, appealing to both action enthusiasts and those seeking meaningful, values-driven storytelling.</t>
         </is>
       </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -22055,6 +23220,11 @@
 The film appeals to audiences seeking substantive, thought-provoking cinema about family dynamics and American identity during a turbulent era.</t>
         </is>
       </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -22146,6 +23316,11 @@
 5. **Cultural Representation** - Serves African American audiences with culturally specific humor and relatable family dynamics
 6. **Multigenerational Appeal** - Bridges age gaps with content that parents and older teens can watch together during the Halloween season
 The film essentially meets the need for accessible, culturally resonant comedy with light seasonal theming and family values.</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -22235,6 +23410,11 @@
 The film serves as easy, undemanding content for parents seeking safe viewing options for elementary-aged children, particularly during winter months or holiday breaks.</t>
         </is>
       </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -22325,6 +23505,11 @@
           <t># Patriots Day: Viewer Desires and Needs Met
 **Patriots Day** (2016) satisfies several key viewer desires:
 **Emotional catharsis** - The film provides closure and collective healing regarding the 2013 Boston Marathon bombing through dramatization of the tragedy and its resolution. **Heroism and resilience** - Viewers witness ordinary people and first responders displaying courage, satisfying the desire to see human goodness triumph over evil. **Patriotic affirmation** - The film reinforces American values of community strength and unity in crisis, appealing to national pride. **Justice fulfillment** - The depiction of the bombers' capture satisfies the need to see wrongdoers held accountable. **Understanding and meaning-making** - It helps audiences process a traumatic national event by providing narrative structure and context to chaotic real-world violence. **Tribute and remembrance** - The film honors victims and survivors, meeting the desire to commemorate and respect those affected.</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -22426,6 +23611,11 @@
 The film primarily serves viewers looking for accessible, violent entertainment with recognizable actors in a conventional crime-revenge framework.</t>
         </is>
       </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22525,6 +23715,11 @@
 The film primarily serves viewers seeking spiritual reassurance during difficult times and those wrestling with faith questions about suffering.</t>
         </is>
       </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -22613,6 +23808,11 @@
       <c r="X248" t="inlineStr">
         <is>
           <t>"How to Be a Latin Lover" meets viewers' desires for lighthearted escapism and wish-fulfillment through its rags-to-riches premise. It satisfies needs for comedic entertainment with physical humor and romantic situations, while also appealing to audiences seeking representation of Latino characters in mainstream comedy. The film offers feel-good family themes about personal growth and redemption, alongside the pleasure of watching a shallow protagonist learn life lessons, providing both laughter and emotional satisfaction without requiring deep engagement.</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -22714,6 +23914,11 @@
 The film targets both nostalgic adult fans and younger audiences seeking accessible superhero entertainment.</t>
         </is>
       </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -22813,6 +24018,11 @@
 - **Hope and resilience**: An ultimately uplifting story about love overcoming significant obstacles</t>
         </is>
       </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -22901,6 +24111,11 @@
       <c r="X251" t="inlineStr">
         <is>
           <t>"Unlocked" (2017) meets viewers' desires for high-stakes espionage thrills, featuring a CIA interrogator racing against time to prevent a biological attack on London. The film satisfies needs for suspenseful action, conspiracy intrigue, and the appeal of watching skilled professionals navigate dangerous double-crosses, while offering the star power of Noomi Rapace, Orlando Bloom, and Michael Douglas in a tense terrorism-prevention narrative.</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -22986,6 +24201,11 @@
 - **Familiar characters** for fans of the Alpha and Omega franchise
 - **Low-stakes entertainment** that parents can use as easy background viewing or to occupy children without concern for inappropriate content
 The film primarily serves as accessible, undemanding content for very young viewers rather than offering sophisticated storytelling or animation quality that might appeal to broader family audiences or animation enthusiasts.</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -23086,6 +24306,11 @@
 The film primarily serves hip-hop enthusiasts and those interested in understanding one of rap's most influential and complex figures.</t>
         </is>
       </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -23162,6 +24387,11 @@
       <c r="X254" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "The Power of the Present" in my knowledge base. This title could refer to a documentary about mindfulness, a spiritual/self-help film, or content related to living in the moment, but without confirmed details about this specific film, I cannot accurately describe what viewer needs it meets. If you could provide additional context (release year, director, or subject matter), I might be able to offer more insight.</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -23261,6 +24491,11 @@
 6. **Geopolitical thriller elements** - Espionage and international intrigue appeal to audiences interested in spy fiction and global conflict narratives</t>
         </is>
       </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -23351,6 +24586,11 @@
           <t># The Glass Castle: Viewer Desires and Needs Met
 **The Glass Castle** (2017) fulfills several key viewer desires:
 **Emotional catharsis** - The film provides a powerful outlet for processing complex family dynamics, childhood trauma, and the struggle to reconcile love for flawed parents. **Inspiration and resilience** - Viewers witness Jeannette Walls' journey from poverty to success, satisfying the need for hope and proof that difficult circumstances can be overcome. **Validation of experience** - For those with unconventional or dysfunctional upbringings, the film offers recognition and normalization of their struggles. **Understanding and forgiveness** - The story explores themes of compassion for imperfect parents, helping viewers grapple with their own family conflicts and the complexity of loving deeply flawed people. **Authentic storytelling** - Based on a true story, it meets the desire for genuine, unvarnished narratives about real human experience rather than idealized family portrayals.</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -23453,6 +24693,11 @@
 The film provides undemanding, fun entertainment that doesn't require emotional investment or deep thought.</t>
         </is>
       </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -23542,6 +24787,11 @@
         <is>
           <t># Summary
 Leatherface meets viewer desires for visceral horror thrills, shock value, and adrenaline through extreme violence and gore. It satisfies curiosity about the origin story of an iconic horror villain, appeals to fans seeking transgressive content that pushes boundaries, and provides cathartic release through controlled fear in a safe environment. The film also fulfills the desire for suspenseful entertainment and the psychological fascination with understanding what creates a monster.</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -23638,6 +24888,11 @@
 The film appeals to audiences interested in Irish history, political thrillers, and true crime stories while providing both entertainment and insight into a significant historical event.</t>
         </is>
       </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -23728,6 +24983,11 @@
           <t># Summary of Viewer Desires Met by *Stronger*
 *Stronger* (2017) fulfills several key viewer needs:
 **Emotional catharsis** - The film provides a space to process trauma and witness resilience through Jeff Bauman's recovery after the Boston Marathon bombing. **Inspiration and hope** - Viewers seeking uplifting narratives find motivation in the protagonist's determination to rebuild his life despite devastating injuries. **Authentic human drama** - The film satisfies desire for realistic, non-sanitized portrayals of disability, PTSD, and family dysfunction rather than simplistic "hero" narratives. **Connection to real events** - It meets the need to understand and memorialize a significant national tragedy through personal perspective. **Relationship dynamics** - The complex romantic and family relationships provide relatable emotional stakes beyond the central trauma story.</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -23825,6 +25085,11 @@
 **Comfort and Familiarity** - For existing fans, continuation of beloved characters and universe they already enjoy</t>
         </is>
       </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23907,6 +25172,11 @@
 The series primarily serves children seeking engaging content while giving parents educational entertainment that supports social-emotional development.</t>
         </is>
       </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -23997,6 +25267,11 @@
           <t>The film Jigsaw meets viewer desires for suspense and puzzle-solving through its mystery-thriller format, satisfies those seeking visceral thrills and gore through its franchise-signature elaborate traps, appeals to fans wanting continuity by expanding the Saw universe lore, and provides cathartic justice fantasies through its premise of punishing morally corrupt characters. The film also delivers plot twists and reveals that reward attentive viewers who enjoy piecing together clues.</t>
         </is>
       </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -24088,6 +25363,11 @@
 *Marrowbone* satisfies viewers seeking atmospheric gothic horror with emotional depth. It appeals to those who enjoy mystery-driven narratives with twists, family drama centered on sibling bonds and protection, and slow-burn psychological tension over jump scares. The film meets desires for visually striking period settings, themes of trauma and secrets, and stories that blend supernatural elements with human tragedy. It particularly resonates with audiences who appreciate melancholic, character-focused horror that prioritizes mood and storytelling over graphic violence.</t>
         </is>
       </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -24176,6 +25456,11 @@
       <c r="X265" t="inlineStr">
         <is>
           <t>"Last Flag Flying" meets viewers' desires for authentic male friendship, emotional catharsis around loss and grief, and thoughtful exploration of how war affects veterans across generations. The film appeals to those seeking mature, character-driven drama that examines themes of loyalty, redemption, and finding meaning after tragedy, while also offering moments of humor and warmth that balance its heavier subject matter. It satisfies audiences looking for nuanced performances and contemplative storytelling rather than action-driven narratives.</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -24276,6 +25561,11 @@
 The film satisfies the need for feel-good, meaningful entertainment that encourages compassion and celebrates human dignity.</t>
         </is>
       </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -24366,6 +25656,11 @@
           <t>"Once Upon a Time at Christmas" is a horror-slasher film that appeals to viewers seeking dark, subversive entertainment that combines holiday themes with gore and violence. It satisfies desires for transgressive content that corrupts traditional Christmas imagery, appeals to horror fans who enjoy seasonal-themed slashers, and offers cathartic thrills through its villain couple dressed as Santa and Mrs. Claus committing brutal murders. The film meets needs for counter-programming against wholesome holiday movies and provides shock value entertainment for audiences drawn to exploitation and grindhouse-style cinema.</t>
         </is>
       </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -24456,6 +25751,11 @@
           <t>"Love Beats Rhymes" (2017) meets viewer desires for an inspirational story about a young woman pursuing her dreams in hip-hop while overcoming personal struggles. The film appeals to audiences seeking representation of Black female artists, authentic hip-hop culture, coming-of-age narratives, and themes of self-expression, resilience, and finding one's voice despite adversity. It satisfies needs for stories about artistic ambition, family dynamics, and empowerment through creativity.</t>
         </is>
       </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -24544,6 +25844,11 @@
       <c r="X269" t="inlineStr">
         <is>
           <t>"Winchester" meets viewer desires for supernatural horror entertainment, particularly appealing to those interested in haunted house stories based on true events. The film satisfies curiosity about the famous Winchester Mystery House and its eccentric heiress Sarah Winchester, while delivering jump scares, gothic atmosphere, and themes of guilt and redemption. It caters to audiences seeking accessible, PG-13 horror with historical intrigue and a mystery-solving narrative structure.</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -24644,6 +25949,11 @@
 The film satisfies audiences interested in thoughtful, adult-oriented dramas that provoke reflection on accountability and cultural collision.</t>
         </is>
       </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -24734,6 +26044,11 @@
           <t>"Acrimony" meets viewers' desires for emotional catharsis through a revenge narrative, offering satisfaction in seeing a wronged woman's rage validated. It appeals to audiences interested in relationship drama, exploring themes of betrayal, sacrifice, and the consequences of unreciprocated loyalty. The film also provides melodramatic entertainment and allows viewers to vicariously experience extreme emotional responses to infidelity and exploitation in marriage.</t>
         </is>
       </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -24822,6 +26137,11 @@
       <c r="X272" t="inlineStr">
         <is>
           <t>"Krystal" (2017) meets viewer desires for coming-of-age romantic comedies with an unconventional twist. The film appeals to audiences seeking heartfelt stories about personal growth, overcoming obstacles (the protagonist joins AA to get closer to his crush despite not being an alcoholic), and awkward but earnest young love. It satisfies those who enjoy quirky indie comedies with eccentric characters, underdog protagonists, and narratives about finding yourself while pursuing romance in unexpected places.</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -24918,6 +26238,11 @@
 The film combines entertainment with social consciousness, allowing viewers to experience excitement while feeling informed about an important humanitarian issue.</t>
         </is>
       </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -25002,6 +26327,11 @@
       <c r="X274" t="inlineStr">
         <is>
           <t>"The Con Is On" (2018) meets viewer desires for lighthearted escapism through a comedic caper about con artists on the run. It appeals to audiences seeking easy entertainment with recognizable stars (Uma Thurman, Tim Roth), glamorous settings, and a playful heist premise that doesn't require serious intellectual engagement. The film caters to those wanting a breezy, low-stakes comedy with elements of crime and deception.</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -25095,6 +26425,11 @@
 - **Provocative humor** - enjoying politically incorrect jokes and boundary-pushing behavior without personal consequences
 - **Underdog satisfaction** - seeing a disillusioned everyman character reclaim agency and joy
 The film provides escapist entertainment for viewers frustrated with conformity and seeking vicarious experiences of radical honesty and hedonistic freedom.</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -25196,6 +26531,11 @@
 The film satisfies viewers seeking thoughtful, character-focused war dramas that prioritize psychological realism over spectacle.</t>
         </is>
       </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -25291,6 +26631,11 @@
 The film primarily satisfies desires for uncomplicated action spectacle rather than narrative depth or character development.</t>
         </is>
       </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -25381,6 +26726,11 @@
           <t>"Uncle Drew" meets viewers' desires for feel-good entertainment, nostalgia, and underdog sports stories. The film delivers comedy through its premise of elderly basketball players (played by NBA legends in age makeup) competing in a street tournament, while satisfying fans' appreciation for basketball legends like Kyrie Irving, Shaquille O'Neal, and Reggie Miller. It provides themes of redemption, second chances, and proving that age doesn't limit ability, along with accessible humor and inspirational messages about teamwork and pursuing dreams that appeal to family audiences and sports fans.</t>
         </is>
       </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -25472,6 +26822,11 @@
 The film satisfies viewers seeking intense action and suspense through its depictions of cross-border violence and covert operations. It appeals to audiences interested in morally complex narratives about the drug war, government tactics, and ethical ambiguity in law enforcement. The film also meets desires for gritty realism, political intrigue, and exploration of contemporary border security issues. Fans of the original Sicario find continuation of Benicio del Toro's compelling character, while action enthusiasts appreciate the tactical combat sequences and tense confrontations in lawless settings.</t>
         </is>
       </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -25560,6 +26915,11 @@
       <c r="X280" t="inlineStr">
         <is>
           <t>"Siberia" (2018) meets viewers' desires for visually stunning cinematography and atmospheric storytelling, appealing to those who appreciate slow-burn, contemplative cinema. The film satisfies needs for escapism through exotic locations, philosophical exploration of isolation and identity, and Keanu Reeves fans seeking his dramatic performance. It also appeals to audiences interested in noir-style thrillers with morally complex characters navigating dangerous situations in unfamiliar territory.</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -25660,6 +27020,11 @@
 The film satisfies cravings for accessible horror that combines teen drama with paranormal scares in a visually striking setting.</t>
         </is>
       </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -25758,6 +27123,11 @@
 The film provides lighthearted entertainment that allows viewers to vicariously experience adventure while laughing at relatable characters navigating absurd situations.</t>
         </is>
       </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -25855,6 +27225,11 @@
 - **Genre comfort** - Provides familiar horror movie conventions for fans of supernatural thrillers</t>
         </is>
       </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -25945,6 +27320,11 @@
           <t>"Little Italy" meets viewer desires for light romantic escapism through its predictable enemies-to-lovers storyline set against a colorful ethnic backdrop. The film appeals to audiences seeking uncomplicated feel-good entertainment with familiar rom-com tropes, food-centric imagery, and nostalgia for traditional Italian-American culture. It satisfies those wanting a low-stakes, easy-to-watch movie that requires minimal emotional investment while delivering comfort through genre conventions and a guaranteed happy ending.</t>
         </is>
       </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -26035,6 +27415,11 @@
           <t>"Kin" (2018) meets viewer desires for science fiction action spectacle, family bonding themes, and coming-of-age storytelling. It appeals to audiences seeking a blend of grounded crime drama with futuristic elements, offering escapist entertainment through its mysterious alien weapon premise while exploring themes of brotherhood, loyalty, and a young protagonist discovering his strength and identity amid dangerous circumstances.</t>
         </is>
       </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -26113,6 +27498,7 @@
           <t>"Norm of the North: Keys to the Kingdom" meets basic viewer needs for lighthearted family entertainment, offering simple humor and colorful animation for young children. The film provides an easy-to-follow adventure story with environmental themes about protecting nature, along with unchallenging content that parents can use to occupy small children with minimal concern about inappropriate material.</t>
         </is>
       </c>
+      <c r="Y286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -26202,6 +27588,11 @@
         <is>
           <t># Summary
 The film *Reprisal* meets viewer desires for justice and catharsis through its revenge thriller narrative. It appeals to audiences seeking action-packed entertainment with a morally straightforward storyline where a protagonist confronts criminals who wronged him. The film satisfies the psychological need to see wrongdoers punished and victims empowered, while delivering suspenseful sequences and dramatic confrontations that provide escapist entertainment and emotional release.</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26303,6 +27694,11 @@
 The film essentially serves viewers wanting a fun, seasonal slasher that captures the haunted house experience.</t>
         </is>
       </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -26371,6 +27767,11 @@
       <c r="X289" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Cursed: The True Nature of Hereditary." You may be thinking of the 2018 horror film "Hereditary" directed by Ari Gaster, which explores themes of family trauma, grief, and inescapable fate. That film meets viewer desires for psychological horror, unsettling atmosphere, strong performances (particularly Toni Collette's), and deeper commentary on how trauma and mental illness pass through generations. If you're referring to a different or related documentary, I don't have information about it in my knowledge base.</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26461,6 +27862,11 @@
 - **Star appeal** of Omar Sy and accessible mainstream French cinema
 - **Easy viewing** requiring minimal intellectual engagement—perfect for relaxation and laughs
 The film appeals to audiences wanting uncomplicated, comedic action with cross-cultural humor.</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26562,6 +27968,11 @@
 The film delivers conventional thriller satisfaction without moral ambiguity or complex politics.</t>
         </is>
       </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -26651,6 +28062,11 @@
         <is>
           <t># Summary of Viewer Desires Met by "Air Strike"
 "Air Strike" appeals to viewers seeking large-scale wartime spectacle and action sequences, particularly those interested in World War II history from a Chinese perspective. The film satisfies desires for patriotic narratives showcasing Chinese resistance against Japanese invasion, features international star power (Bruce Willis), and delivers explosive aerial combat and disaster sequences. It meets needs for heroic sacrifice stories and dramatic wartime survival tales set during the bombing of Chongqing.</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26751,6 +28167,11 @@
 - **Nostalgia**: Connection to a beloved folk legend and cultural mythology</t>
         </is>
       </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -26839,6 +28260,11 @@
       <c r="X294" t="inlineStr">
         <is>
           <t>"The Super" (1991) meets viewer desires for wish-fulfillment comedy and social justice by depicting a slumlord forced to live in his own neglected building, satisfying audiences' need to see exploitation punished, the powerful humbled, and underprivileged tenants empowered. The film provides comedic entertainment while addressing real concerns about housing inequality and absentee landlords getting their comeuppance.</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26936,6 +28362,11 @@
 - **Relatable relationship themes** about learning from past errors and personal growth
 - **Feel-good storytelling** with humor and heart, offering comfort that mistakes can lead to better outcomes
 The film satisfies desires for both genre entertainment (time travel) and emotional connection (romance and redemption).</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -27028,6 +28459,11 @@
 The film satisfies audiences looking for genuine, transformative stories that restore faith in humanity.</t>
         </is>
       </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -27118,6 +28554,11 @@
           <t>"Ben Is Back" meets viewers' desires for emotionally intense family dramas that explore addiction, redemption, and unconditional parental love. The film appeals to audiences seeking authentic portrayals of the opioid crisis's impact on families, suspenseful storytelling driven by a ticking-clock premise (one day/night), and powerful performances that showcase the complexities of recovery and relapse. It satisfies those looking for stories about forgiveness, maternal devotion, and the difficult realities of supporting loved ones struggling with substance abuse.</t>
         </is>
       </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -27207,6 +28648,11 @@
         <is>
           <t># Summary
 *Leprechaun Returns* meets viewer desires for nostalgic horror-comedy entertainment, providing campy fun through over-the-top gore, dark humor, and self-aware B-movie charm. It appeals to fans seeking lighthearted slasher thrills without serious scares, offering escapist entertainment through absurd kills, practical effects nostalgia, and the comfort of a familiar franchise formula. The film satisfies cravings for guilty pleasure horror that doesn't take itself seriously.</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -27306,6 +28752,11 @@
 The film satisfies audiences looking for low-stakes, formulaic crime action rather than innovative or critically acclaimed cinema.</t>
         </is>
       </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -27396,6 +28847,11 @@
           <t>"Long Shot" meets viewer desires for romantic escapism, wish-fulfillment fantasy, and comedic entertainment. The film satisfies the need for feel-good storytelling through its unlikely romance between a powerful politician and an ordinary journalist, offering both laughs and optimism. It also appeals to audiences seeking social commentary wrapped in accessible humor, touching on political themes while maintaining a lighthearted tone that provides stress relief and emotional satisfaction through its ultimately uplifting message about authenticity and love.</t>
         </is>
       </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -27484,6 +28940,11 @@
       <c r="X301" t="inlineStr">
         <is>
           <t>"Life Like" (2019) meets viewer desires for science fiction exploration of artificial intelligence and human-robot relationships, offering suspense and ethical questions about the boundaries between humans and lifelike androids. The film appeals to audiences interested in technological thrillers, moral dilemmas about AI consciousness, and the potential dangers of creating too-realistic artificial beings, while also providing elements of psychological tension and dark drama.</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -27585,6 +29046,11 @@
 The film primarily appeals to action enthusiasts seeking high-quality, stylish entertainment with minimal complex narrative demands.</t>
         </is>
       </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -27667,6 +29133,11 @@
           <t>"Project Ithaca" appeals to viewers who enjoy science fiction thrillers with contained settings, alien mysteries, and survival scenarios. The film satisfies desires for puzzle-box narratives where strangers must work together to escape captivity aboard an alien spacecraft, combining elements of body horror, conspiracy theories, and action. It attracts audiences seeking B-movie entertainment with modest production values that focus on tension and paranoia rather than big-budget spectacle.</t>
         </is>
       </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -27749,6 +29220,7 @@
           <t>"Norm of the North: King Sized Adventure" meets viewer desires for family-friendly entertainment, particularly for young children. It provides lighthearted comedy, colorful animation, and simple moral lessons about friendship, responsibility, and environmentalism. The film offers parents an easy, non-threatening viewing option that keeps children entertained with slapstick humor and adventure while delivering safe, positive messages. It fulfills the need for accessible, low-stakes content that requires minimal parental guidance.</t>
         </is>
       </c>
+      <c r="Y304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -27829,6 +29301,11 @@
       <c r="X305" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Step Up: Year of the Dance." This doesn't appear to be part of the Step Up franchise. The Step Up movies include titles like "Step Up," "Step Up 2: The Streets," "Step Up 3D," "Step Up Revolution," and "Step Up: All In," but not one with "Year of the Dance" in the title. You may be thinking of a different film or possibly confusing the title with another dance movie.</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -27929,6 +29406,11 @@
 The film primarily serves viewers who appreciate thought-provoking, uncomfortable cinema over traditional narrative satisfaction.</t>
         </is>
       </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -28014,6 +29496,11 @@
         <is>
           <t># Summary
 *3 from Hell* meets viewer desires for extreme horror, visceral violence, and transgressive entertainment. Fans of Rob Zombie's work seek his signature gritty aesthetic, dark humor, and continuation of beloved characters from *The Devil's Rejects*. The film appeals to audiences craving shocking content, anti-hero narratives, exploitation cinema nostalgia, and unapologetic gore that pushes boundaries of mainstream horror. It satisfies desires for cathartic violence, counter-cultural rebellion, and the pleasure of watching charismatic villains defy death and authority.</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -28110,6 +29597,11 @@
 The film meets needs for both visceral action entertainment and thoughtful drama about sacrifice and ethical complexity.</t>
         </is>
       </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -28207,6 +29699,11 @@
 - **Underdog story** - Follows a socially inept character's journey to self-improvement and romance</t>
         </is>
       </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -28283,6 +29780,11 @@
       <c r="X310" t="inlineStr">
         <is>
           <t>"Arctic Dogs" meets viewers' desires for lighthearted family entertainment with colorful animation, slapstick humor, and a simple underdog story. It appeals to young children seeking adventure with talking animals, while providing parents with an inoffensive, predictable viewing experience that requires minimal emotional investment.</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -28383,6 +29885,11 @@
 The film appeals to audiences who prefer thoughtful, restrained spy dramas over action-heavy thrillers.</t>
         </is>
       </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -28473,6 +29980,11 @@
           <t>"Berlin, I Love You" meets viewer desires for romantic escapism, cultural exploration of Berlin through multiple perspectives, and anthology-style storytelling that offers varied emotional experiences. The film appeals to audiences seeking glimpses of different types of love and human connection set against the backdrop of a cosmopolitan European city, similar to other films in the "Cities of Love" franchise.</t>
         </is>
       </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -28562,6 +30074,11 @@
         <is>
           <t># Summary
 "Trauma Center" meets viewer desires for action-thriller entertainment, featuring elements like suspense, violence, and a cat-and-mouse pursuit. The film appeals to audiences seeking straightforward genre entertainment with Bruce Willis, corrupt-cop conspiracies, witness-in-peril scenarios, and tension-building sequences. It satisfies needs for escapist entertainment, crime drama thrills, and the gratification of seeing justice served against villainous antagonists.</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -28663,6 +30180,11 @@
 The film satisfies audiences wanting meaningful stories about real-world issues while providing entertainment value through compelling drama and performances.</t>
         </is>
       </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -28754,6 +30276,11 @@
 "Primal" satisfies audiences seeking visceral action and survival thrills through its premise of a big-game hunter and a captured jaguar forced to work together aboard a ship filled with deadly released animals and a political assassin. The film appeals to fans of Nicolas Cage's intense performances, delivers straightforward action entertainment without complex plotting, and provides escapist spectacle through its contained setting and man-versus-beast conflicts. It meets the desire for B-movie creature features with practical tension and violence.</t>
         </is>
       </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -28840,6 +30367,11 @@
           <t>"Vanguard" (2020) meets viewers' desires for high-octane action entertainment through its elaborate stunts, exotic international locations, and fast-paced chase sequences. The film provides escapist entertainment with Jackie Chan's signature blend of martial arts and comedy, while delivering straightforward heroic narratives where good triumphs over evil. It appeals to audiences seeking visually spectacular set pieces, including jet ski battles and luxury car chases, without requiring deep emotional investment or complex storytelling.</t>
         </is>
       </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -28922,6 +30454,7 @@
           <t>**Norm of the North: Family Vacation** meets the desires of parents seeking inoffensive, easy-to-access entertainment for very young children (typically preschool to early elementary age). The film provides simple humor, colorful animation, familiar characters, and straightforward moral lessons about family and togetherness. It serves as a low-stakes viewing option that requires minimal parental supervision and keeps kids occupied for a brief period, though it doesn't aim to satisfy viewers seeking quality storytelling, sophisticated animation, or content that appeals to older audiences or adults.</t>
         </is>
       </c>
+      <c r="Y317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -29012,6 +30545,11 @@
           <t>"I Still Believe" meets viewers' desires for inspirational faith-based content, romantic love stories, and emotional catharsis through tragedy. It appeals to Christian audiences seeking films that reinforce their beliefs, fans of true stories about overcoming adversity, and those who enjoy tearjerker romances centered on young love tested by terminal illness. The film provides hope, spiritual affirmation, and an emotionally moving experience for viewers who want uplifting content that explores themes of faith, loss, and perseverance.</t>
         </is>
       </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -29099,6 +30637,11 @@
 *Made in Italy* meets viewers' desires for heartwarming family reconciliation stories, beautiful Italian scenery as visual escapism, themes of healing from grief and loss, nostalgia for simpler times, and the appeal of watching a real-life father-son duo (Liam and Micheál Neeson) navigate an emotionally authentic relationship on screen. The film provides comfort through its gentle pacing, romantic Tuscan settings, and uplifting message about new beginnings after tragedy.</t>
         </is>
       </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -29187,6 +30730,11 @@
       <c r="X320" t="inlineStr">
         <is>
           <t>"Rogue" meets viewers' desires for suspenseful nature horror, featuring a giant crocodile terrorizing tourists in the Australian outback. The film satisfies audiences seeking creature-feature thrills, survival tension, beautiful yet dangerous wilderness cinematography, and visceral predator-versus-human confrontations with practical effects and jump scares.</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -29287,6 +30835,7 @@
 The film primarily attracts viewers interested in socially conscious horror/thriller content that explores racial injustice through a genre lens.</t>
         </is>
       </c>
+      <c r="Y321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -29376,6 +30925,11 @@
         <is>
           <t># Summary
 **Guest House** (2020) meets viewer desires for raunchy, lowbrow comedy through outrageous sexual humor, crude gags, and over-the-top party antics. It appeals to audiences seeking mindless escapism, slapstick physical comedy, and boundary-pushing jokes without requiring emotional investment or complex storytelling. The film caters to fans of Pauly Shore's comedy style and those looking for a light, no-stakes entertainment experience centered on wild behavior and absurd situations.</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -29457,6 +31011,11 @@
 The film meets the need for thoughtful, anti-commercial cinema that critiques capitalist structures while celebrating human connection, dignity, and resourcefulness in the face of systemic injustice.</t>
         </is>
       </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -29543,6 +31102,7 @@
           <t>"The Doorman" satisfies viewers seeking straightforward action entertainment with a female protagonist. It appeals to fans of Die Hard-style single-location thrillers, offering wish-fulfillment through a protective hero defending innocent people against criminals. The film meets desires for redemption narratives, physical combat sequences, and underdog triumph stories, while providing accessible, uncomplicated escapist entertainment that doesn't require deep emotional investment.</t>
         </is>
       </c>
+      <c r="Y324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -29642,6 +31202,11 @@
 The film targets audiences who enjoy destination horror, paranoid thrillers, and stories about Western tourists confronting sinister local customs.</t>
         </is>
       </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -29740,6 +31305,11 @@
 The film appeals to audiences seeking comforting, life-affirming entertainment during the holiday season.</t>
         </is>
       </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -29827,6 +31397,11 @@
 "The Very Excellent Mr. Dundee" meets viewer desires for lighthearted, nostalgic entertainment by featuring Paul Hogan playing a fictionalized version of himself dealing with comic misfortunes that threaten his knighthood. The film appeals to fans of the original "Crocodile Dundee" franchise seeking familiar faces and self-deprecating humor, while offering easy-to-watch comedy that doesn't require much intellectual investment. It satisfies the need for feel-good escapism and celebrity cameos in a low-stakes narrative about reputation and redemption.</t>
         </is>
       </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -29918,6 +31493,11 @@
 **Wrong Turn** meets viewer desires for visceral thrills and survival horror through its depiction of isolated protagonists hunted by cannibalistic mountain dwellers. The film satisfies audiences seeking intense gore, jump scares, and suspenseful cat-and-mouse scenarios. It also appeals to those who enjoy cautionary tales about venturing into unknown territory, the primal fear of being prey, and the cathartic experience of watching characters fight for survival against overwhelming odds. The formulaic slasher elements provide familiar genre pleasures while the backwoods setting taps into deep-seated anxieties about civilization versus savagery.</t>
         </is>
       </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -30006,6 +31586,11 @@
       <c r="X329" t="inlineStr">
         <is>
           <t>"Smiley Face Killers" appeals to viewers seeking thriller/horror entertainment, particularly those interested in true crime conspiracy theories. The film satisfies desires for suspense, violence, and dark mystery while exploring the urban legend of a serial killer network. It caters to audiences who enjoy slasher films, paranoid thrillers, and content based on real-world unsolved cases, offering both fear-based entertainment and engagement with controversial investigative theories.</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30089,6 +31674,11 @@
 The film appeals to audiences seeking both entertainment and emotional resonance in contemporary romance.</t>
         </is>
       </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -30157,6 +31747,11 @@
       <c r="X331" t="inlineStr">
         <is>
           <t>"Coronavirus Conspiracy" appeals to viewers seeking alternative explanations for the COVID-19 pandemic, particularly those skeptical of official narratives. It meets desires for validation of distrust in government and mainstream media, offers a sense of "insider knowledge" or "truth-seeking," and provides community connection with like-minded individuals who question established institutions and pandemic responses.</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30255,6 +31850,11 @@
 - **Crime procedural** satisfaction following DEA investigation tactics
 - **Cautionary tale** about idealism corrupted by power and greed
 The film meets needs for entertainment that combines technology, crime, and contemporary relevance while examining the human costs of operating outside the law.</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30356,6 +31956,11 @@
 The film satisfies audiences looking for a fast-paced, visually engaging sci-fi story with romantic and emotional elements aimed primarily at teen and young adult demographics.</t>
         </is>
       </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -30446,6 +32051,11 @@
           <t>"Dark Web: Cicada 3301" appeals to viewers interested in cyber-thrillers and puzzle-solving mysteries. It satisfies desires for tech-savvy storytelling, cryptography intrigue, and conspiracy narratives centered around the real-world internet phenomenon of the same name. The film targets audiences who enjoy hacker culture, digital treasure hunts, and dark web aesthetics, offering escapist entertainment for those fascinated by underground online communities and elaborate enigmas that blend technology with secretive organizations.</t>
         </is>
       </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -30537,6 +32147,11 @@
 *Barb &amp; Star Go to Vista Del Mar* meets viewers' desires for lighthearted escapism, absurdist comedy, and feel-good entertainment. The film provides nostalgia through its vibrant, retro aesthetic and celebrates female friendship without drama or competition. It offers pure silliness and campy humor that doesn't require deep analysis, serving as colorful comfort viewing. The musical numbers, tropical setting, and intentionally ridiculous plot give audiences permission to enjoy something unabashedly fun and strange, filling a need for comedy that embraces weirdness while remaining fundamentally optimistic and heartwarming.</t>
         </is>
       </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -30623,6 +32238,11 @@
           <t>"The Penthouse" (1967) is an exploitation thriller that primarily appealed to viewers seeking provocative content, sexual titillation, and violence within a suspenseful home invasion scenario. The film met desires for taboo-breaking entertainment during a period of changing censorship standards, offering voyeuristic thrills, danger, and the psychological tension of criminals terrorizing victims in a confined setting. It catered to audiences interested in edgier, more adult-oriented content that pushed boundaries of what was acceptable in mainstream cinema at the time.</t>
         </is>
       </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -30707,6 +32327,11 @@
       <c r="X337" t="inlineStr">
         <is>
           <t>"The Virtuoso" appeals to viewers who enjoy moody, atmospheric thriller experiences with a solitary assassin protagonist. It meets desires for suspenseful cat-and-mouse narratives, minimalist noir storytelling with sparse dialogue, and the appeal of watching a methodical professional operate under pressure. The film caters to fans of Anthony Hopkins in mentor roles and audiences seeking tense, puzzle-like mysteries where they can try to deduce answers alongside the protagonist in a remote, claustrophobic setting.</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30808,6 +32433,11 @@
 The film essentially revitalizes a familiar franchise while tapping into contemporary social issues and mainstream appeal.</t>
         </is>
       </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -30888,6 +32518,11 @@
       <c r="X339" t="inlineStr">
         <is>
           <t>"The House Next Door: Meet the Blacks 2" meets viewer desires for lowbrow comedy and parody entertainment. It appeals to audiences seeking slapstick humor, crude jokes, and satirical takes on the horror genre, particularly spoofing "The Purge" franchise. The film caters to fans of the first "Meet the Blacks" movie and those who enjoy Mike Epps' comedic style, offering escapist entertainment through exaggerated situations, physical comedy, and social commentary wrapped in farce. It satisfies viewers looking for undemanding, lighthearted content that doesn't require serious emotional or intellectual engagement.</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30987,6 +32622,11 @@
 The film functions as comfort food cinema—predictable, energetic, and designed purely for fun rather than artistic ambition.</t>
         </is>
       </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -31073,6 +32713,11 @@
           <t>"Die in a Gunfight" appeals to viewers seeking a stylized, modern romantic action film that combines star-crossed lovers with dark comedy and violence. It satisfies desires for visually striking cinematography, forbidden romance reminiscent of Romeo and Juliet, energetic fight sequences, and a rebellious, edgy tone. The film targets audiences who enjoy irreverent storytelling, anti-hero protagonists, and a blend of romance with criminal underworld drama.</t>
         </is>
       </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -31147,6 +32792,11 @@
           <t>I don't have specific information about a film called "Fin" to provide an accurate summary of what viewer desires or needs it meets. There are several films with this title or similar names from different years and countries. Without knowing which specific film you're referring to (director, year, country of origin), I cannot give you a reliable answer about its appeal to viewers.</t>
         </is>
       </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -31235,6 +32885,11 @@
       <c r="X343" t="inlineStr">
         <is>
           <t>"Midnight in the Switchgrass" appeals to viewers who enjoy crime thrillers based on true events, particularly those interested in serial killer investigations. The film meets desires for suspenseful cat-and-mouse narratives, gritty law enforcement procedurals, and stories about pursuing justice for victims. It also attracts audiences drawn to star power (Bruce Willis, Megan Fox) and those who appreciate darker, violent content exploring the disturbing world of criminal predators targeting vulnerable women.</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -31327,6 +32982,7 @@
 The film targets audiences seeking unchallenging, pleasant viewing experiences with clear moral lessons.</t>
         </is>
       </c>
+      <c r="Y344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -31423,6 +33079,11 @@
 - **Exotic locations**: Globe-trotting espionage across Vietnam, London, and other international settings
 - **Female empowerment**: A capable, intelligent female lead who dominates action sequences
 - **Escapist entertainment**: Stylish, fast-paced thriller providing distraction from everyday life</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -31520,6 +33181,11 @@
 The film appeals to viewers wanting thoughtful, atmospheric horror that uses the vampire metaphor to explore addiction and codependency.</t>
         </is>
       </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -31602,6 +33268,7 @@
           <t>"Jurassic Hunt" appeals to viewers seeking low-budget action entertainment featuring dinosaurs and survival scenarios. It satisfies desires for creature-feature thrills, B-movie camp, and straightforward predator-versus-human conflict without requiring significant intellectual investment. The film caters to audiences who enjoy direct-to-video monster movies and aren't concerned with scientific accuracy or high production values.</t>
         </is>
       </c>
+      <c r="Y347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -31692,6 +33359,11 @@
           <t>"Notorious Nick" meets viewers' desires for inspirational sports stories and overcoming adversity. The film appeals to audiences seeking uplifting true stories about perseverance, as it follows Nick Newell, a one-armed MMA fighter who defied expectations to pursue his dreams in professional fighting. It satisfies needs for underdog narratives, disability representation, and motivational content about triumph over physical limitations.</t>
         </is>
       </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -31778,6 +33450,11 @@
           <t>"The Gateway" meets viewers' desires for gritty crime drama and redemption stories. It appeals to those seeking tense thriller elements, morally complex characters, and narratives about flawed individuals attempting to rebuild their lives while being pulled back into dangerous circumstances. The film satisfies audiences interested in neo-noir aesthetics, family dynamics under pressure, and the consequences of past choices.</t>
         </is>
       </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -31864,6 +33541,11 @@
           <t>"Catch the Bullet" meets viewer desires for classic Western action entertainment, featuring gunfights, frontier justice, and a revenge-driven plot. It appeals to audiences seeking straightforward action sequences, traditional good-versus-evil storytelling, and nostalgic Western genre elements including outlaws, marshals, and rugged landscapes. The film also satisfies those looking for family-oriented themes involving protection and redemption within an accessible, formulaic Western framework.</t>
         </is>
       </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -31946,6 +33628,11 @@
           <t>"The Good House" meets viewers' desires for character-driven drama featuring complex, flawed protagonists navigating real-life struggles. It appeals to audiences seeking stories about addiction, redemption, and second chances, particularly centered on a mature female lead. The film satisfies those interested in intimate small-town dynamics, realistic portrayals of alcoholism, romance later in life, and nuanced performances that explore vulnerability and personal transformation without melodrama.</t>
         </is>
       </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -32036,6 +33723,11 @@
           <t>"Lady of the Manor" (2021) meets viewer desires for lighthearted comedy entertainment, combining elements of fish-out-of-water humor, supernatural friendship, and feel-good redemption. The film appeals to audiences seeking escapist fun with a simple premise about a slacker who befriends a ghost, offering nostalgic mansion settings, mild humor, and an uplifting message about personal growth without requiring deep emotional investment.</t>
         </is>
       </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -32115,6 +33807,11 @@
 *The Jesus Music* meets viewers' desires for nostalgia, spiritual inspiration, and understanding of contemporary Christian music's origins. It appeals to those seeking to connect with their faith through music history, validates the experiences of long-time CCM fans, and satisfies curiosity about how the genre evolved from counterculture roots to mainstream success. The documentary fulfills needs for community belonging among Christian audiences and offers insights into how faith and popular culture intersect.</t>
         </is>
       </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -32193,6 +33890,11 @@
           <t>"The Amityville Moon" appeals to viewers seeking low-budget horror entertainment, particularly fans of werewolf films and the Amityville franchise. It satisfies desires for supernatural scares, creature feature thrills, and the familiar branding of the Amityville name, while catering to audiences who enjoy B-movie horror with modest expectations for production values and storytelling.</t>
         </is>
       </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -32277,6 +33979,11 @@
       <c r="X355" t="inlineStr">
         <is>
           <t>"Survive the Game" meets viewers' desires for action-packed entertainment featuring a tense cat-and-mouse thriller. It appeals to fans of Bruce Willis, delivers straightforward good-vs-evil conflict, provides escapist violence and gunfights, and satisfies those seeking a low-stakes, formulaic action film where an everyday person must protect their family from criminals in a contained, rural setting.</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -32376,6 +34083,11 @@
 The film satisfies those wanting a blend of sci-fi concept and intimate character study about the lengths people go to protect their most valued relationships.</t>
         </is>
       </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -32462,6 +34174,11 @@
           <t>"Last Shoot Out" (also known as "Showdown at Williams Creek") meets viewer desires for classic Western action and justice themes. The film appeals to audiences seeking frontier adventure, tales of moral courage, and the satisfaction of seeing lawmen confront outlaws in a small mining town setting. It provides escapist entertainment through its portrayal of the Old West, features traditional shootout sequences, and delivers the archetypal conflict between good and evil that Western genre fans expect.</t>
         </is>
       </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -32552,6 +34269,11 @@
           <t>"Christmas Is Canceled" meets viewers' desires for lighthearted holiday entertainment with themes of family dynamics, romantic comedy, and personal growth. The film appeals to audiences seeking feel-good escapism during the Christmas season, featuring relatable parent-child conflicts, second chances at love, and ultimately heartwarming resolutions that celebrate family bonds and the spirit of the holidays.</t>
         </is>
       </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -32636,6 +34358,11 @@
       <c r="X359" t="inlineStr">
         <is>
           <t>"Pinocchio: A True Story" (2021) is a Russian animated film that attempts to meet viewer desires for family-friendly entertainment, nostalgia for the classic Pinocchio tale, colorful animation, simple moral lessons about honesty and being true to oneself, and lighthearted adventure suitable for young children. However, the film received largely negative reviews for its poor execution, suggesting it failed to adequately satisfy most viewers' expectations for quality storytelling and animation.</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -32738,6 +34465,11 @@
 The film primarily appeals to audiences seeking uplifting, values-driven entertainment with a clear moral message about faith, determination, and family.</t>
         </is>
       </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -32828,6 +34560,11 @@
           <t>"Shattered" (1991) meets viewer desires for psychological thriller entertainment through its amnesia-driven mystery plot, where audiences piece together clues alongside the protagonist to uncover his true identity and a web of deception. The film satisfies needs for suspense, plot twists, and the intellectual engagement of solving a puzzle, while also delivering on expectations for noir-style drama involving betrayal, conspiracy, and shocking revelations.</t>
         </is>
       </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -32918,6 +34655,11 @@
           <t>"The King's Daughter" meets viewers' desires for family-friendly fantasy entertainment, offering escapism through a magical historical adventure with romance, mermaids, and palace intrigue. It appeals to audiences seeking visually appealing costumes and settings, a feel-good story with themes of compassion and environmental harmony, and light entertainment suitable for children and families without intense violence or mature content.</t>
         </is>
       </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -33006,6 +34748,11 @@
       <c r="X363" t="inlineStr">
         <is>
           <t>Moonfall meets viewers' desires for large-scale disaster spectacle, apocalyptic thrills, and escapist entertainment. The film delivers massive destruction sequences, a high-concept sci-fi premise involving the moon crashing into Earth, and the satisfying formula of underdogs saving humanity against impossible odds. It appeals to audiences seeking popcorn entertainment with visual effects-driven action rather than deep character development or scientific accuracy.</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -33102,6 +34849,11 @@
 7. **American Dream narrative** - Reinforces belief in opportunity and self-made success</t>
         </is>
       </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -33184,6 +34936,11 @@
           <t>"Desperate Riders" meets viewers' desires for classic Western action and adventure, featuring outlaws, gunfights, frontier justice, and themes of survival and redemption in the Old West. It appeals to fans seeking straightforward action entertainment with traditional Western genre elements like horseback chases, lawlessness, and rugged individualism.</t>
         </is>
       </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -33260,6 +35017,11 @@
       <c r="X366" t="inlineStr">
         <is>
           <t>**C.I.Ape** meets viewers' desires for lighthearted, family-friendly entertainment through absurdist comedy. The film appeals to those seeking escapist fun with a ridiculous premise (a chimpanzee secret agent), slapstick humor, and simple action-adventure storytelling that doesn't require serious engagement. It satisfies the need for nostalgic, B-movie style entertainment and provides easy viewing for children or adults looking for "so-bad-it's-good" comedy without complex plots or heavy themes.</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -33361,6 +35123,11 @@
 The film provides comfortable, undemanding entertainment for viewers seeking pleasant distraction rather than challenging cinema.</t>
         </is>
       </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -33451,6 +35218,11 @@
           <t>**Private Property** (1960) meets viewer desires for psychological suspense and transgressive content. The film appeals to audiences interested in exploring taboo themes of obsession, class resentment, and sexual tension through its story of two drifters who target a wealthy housewife. It satisfies desires for noir-influenced cinema that examines darker aspects of human nature, suburban malaise, and the erosion of post-war American idealism, while offering voyeuristic thrills through its provocative and morally ambiguous narrative.</t>
         </is>
       </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -33533,6 +35305,7 @@
           <t>I don't have any information about a film called "Where the Scary Things Are." You may be thinking of "Where the Wild Things Are" (2009), which meets viewers' desires for nostalgia, imaginative escapism, and exploration of childhood emotions like anger, loneliness, and the need for belonging. If you're referring to a different film, I'm not familiar with it.</t>
         </is>
       </c>
+      <c r="Y369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -33601,6 +35374,11 @@
       <c r="X370" t="inlineStr">
         <is>
           <t>This documentary/making-of film meets viewers' desires for behind-the-scenes insight into the creative process of the acclaimed movie "Everything Everywhere All at Once." It satisfies curiosity about how the film's complex multiverse concept, innovative visual effects, and emotional story were developed on a limited budget. The film appeals to fans wanting deeper understanding of the Daniels' directorial vision, the cast's performances (particularly Michelle Yeoh's), and the technical craftsmanship that made the original film such a cultural phenomenon.</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -33693,6 +35471,11 @@
 The film primarily targets younger audiences interested in gaming culture and viewers seeking accessible, positive representations of women in competitive spaces.</t>
         </is>
       </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -33783,6 +35566,11 @@
 - **Emotional depth** - Provides mature reflection on mortality, friendship, and aging that resonates with the original audience now in middle age
 - **Closure** - Offers a heartfelt conclusion to the trilogy for long-time fans
 - **Authentic indie spirit** - Maintains the low-budget, dialogue-driven style that defined the original while addressing real-life struggles of independent artists</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -33875,6 +35663,11 @@
 The film primarily serves audiences seeking undemanding action entertainment with a recognizable star rather than innovative storytelling or artistic merit.</t>
         </is>
       </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -33963,6 +35756,11 @@
       <c r="X374" t="inlineStr">
         <is>
           <t>"Prey for the Devil" meets viewer desires for supernatural horror entertainment, specifically appealing to audiences interested in exorcism themes and religious horror. The film satisfies needs for suspenseful thrills, jump scares, and demonic possession narratives while also potentially attracting viewers interested in seeing a female protagonist in a traditionally male-dominated role (exorcist). It caters to fans of the horror genre seeking accessible, mainstream scares with Catholic Church mysticism and good-versus-evil battles.</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -34052,6 +35850,11 @@
 The film primarily serves viewers wanting uncomplicated, formulaic action content rather than cinematic innovation or depth.</t>
         </is>
       </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -34142,6 +35945,11 @@
           <t>"Mindcage" appeals to viewers who enjoy psychological crime thrillers with cat-and-mouse dynamics between detectives and serial killers. It satisfies desires for suspenseful murder mysteries, puzzle-solving narratives, and the familiar trope of consulting an imprisoned criminal mastermind (similar to "Silence of the Lambs"). The film targets audiences seeking twisty plots, dark atmosphere, and the intellectual challenge of trying to solve the case alongside the protagonists.</t>
         </is>
       </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -34230,6 +36038,11 @@
       <c r="X377" t="inlineStr">
         <is>
           <t>"Alice, Darling" meets viewers' desires for realistic portrayals of psychological abuse and emotional manipulation in relationships. The film appeals to those seeking nuanced depictions of gaslighting, codependency, and the difficult process of recognizing toxic partnerships. It also satisfies audiences looking for character-driven dramas about female friendship as a source of strength and support during personal crisis, while offering validation to viewers who have experienced similar controlling relationships.</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -34322,6 +36135,11 @@
 - **Escapism** - Offers a simple, feel-good narrative that provides stress-free viewing for both kids and adults seeking uncomplicated entertainment</t>
         </is>
       </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -34414,6 +36232,11 @@
 1. **Nostalgia and Historical Interest** - Depicts the 1970s Jesus Movement, appealing to those who lived through it or are curious about this cultural/religious phenomenon. 2. **Inspirational Faith Content** - Provides an uplifting spiritual narrative for Christian audiences seeking affirming, faith-based entertainment. 3. **Counterculture and Rebellion Themes** - Explores hippie culture and generational conflict, attracting viewers interested in stories about social transformation and challenging establishment norms. 4. **Hope and Redemption** - Offers messages of personal transformation, second chances, and finding purpose, meeting emotional needs for optimism. 5. **Community and Belonging** - Shows characters finding acceptance and connection, resonating with viewers' desires for meaningful relationships and spiritual community. 6. **Escapism with Substance** - Delivers entertainment that feels meaningful rather than purely commercial, satisfying audiences wanting films with positive messages and moral clarity.</t>
         </is>
       </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -34506,6 +36329,11 @@
 **Spectacle and Action**: Delivers elaborate, expertly choreographed fight sequences and stunning visuals that provide pure cinematic escapism. **Justice and Catharsis**: Fulfills the desire to see a wronged protagonist fight against overwhelming odds and corrupt systems, offering vicarious satisfaction. **Aesthetic Pleasure**: Provides beautifully composed shots, creative set pieces, and stylized violence that appeal to viewers seeking artistic action cinema. **Simplicity**: Offers straightforward good-vs-evil storytelling that's easy to follow despite its scale, allowing viewers to relax and enjoy without complex moral ambiguity. **Competence Fantasy**: Shows a supremely skilled protagonist who excels at what he does, appealing to desires for mastery and capability. **Emotional Resolution**: Provides closure to a character's journey, satisfying viewers invested in the series arc. The film essentially meets needs for entertainment, escapism, visual artistry, and emotional payoff through highly stylized action filmmaking.</t>
         </is>
       </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -34598,6 +36426,11 @@
 **Nostalgia and Recognition**: Adults who grew up reading Judy Blume's beloved novel find comfort in seeing this cherished story faithfully adapted, reconnecting with their own coming-of-age experiences. **Representation and Validation**: Young viewers, particularly girls, see their real anxieties about puberty, fitting in, and identity reflected on screen in an honest, non-sensationalized way. **Intergenerational Connection**: The film creates opportunities for parents and children to discuss difficult topics like bodily changes, religion, and belonging in a more accessible way. **Authentic Female Experience**: Audiences seeking genuine portrayals of girlhood appreciate the film's candid treatment of menstruation, bra-shopping, and peer pressure without embarrassment or comedy at girls' expense. **Religious/Spiritual Exploration**: Viewers grappling with questions of faith and identity connect with Margaret's personal spiritual journey that doesn't prescribe answers. **Comfort and Reassurance**: The film provides emotional support</t>
         </is>
       </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -34686,6 +36519,11 @@
       <c r="X382" t="inlineStr">
         <is>
           <t>"About My Father" meets viewer desires for lighthearted family comedy, fish-out-of-water humor, and cross-cultural clash entertainment. It appeals to audiences seeking feel-good escapism, relatable family dynamics, and the comedic talents of Sebastian Maniscalco and Robert De Niro. The film satisfies needs for accessible, PG-13 comedy that explores themes of family acceptance, generational differences, and cultural identity without requiring heavy emotional investment.</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -34786,6 +36624,11 @@
 The film appeals to fans of contained thrillers who enjoy accessible scares without supernatural elements.</t>
         </is>
       </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -34884,6 +36727,11 @@
 The film targets audiences who enjoy folk horror aesthetics, parental gaslighting themes, and twisted fairy tale subversions with a dark, unsettling conclusion.</t>
         </is>
       </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -34978,6 +36826,11 @@
 The film primarily serves audiences seeking lighthearted, culturally diverse romantic escapism.</t>
         </is>
       </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -35061,6 +36914,11 @@
 *The Engineer* appeals to viewers seeking intense geopolitical thrilding action, particularly those interested in Israeli-Palestinian conflict narratives. It satisfies desires for revenge-driven plots, espionage tradecraft, and moral complexity in counterterrorism stories. The film meets needs for visceral action sequences combined with real-world historical context, appealing to audiences who appreciate fact-based thrillers exploring the costs of violence and the cycle of retribution in the Middle East conflict.</t>
         </is>
       </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -35151,6 +37009,11 @@
           <t>"Puppy Love" meets viewers' desires for lighthearted romantic entertainment, emotional warmth, and escapism through its charming story about love and companionship. The film appeals to audiences seeking feel-good content, relatable relationship dynamics, and the universal appeal of cute animals (puppies) that bring people together, offering comfort and optimism about finding connection and romance.</t>
         </is>
       </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -35245,6 +37108,11 @@
 - **Testosterone-fueled violence**: Satisfies appetite for explosive gunfights, hand-to-hand combat, and military-style missions
 - **Franchise loyalty**: Continues a familiar series for fans invested in the characters and formula
 - **Simplistic good vs. evil**: Offers straightforward plot with clear heroes and villains requiring minimal thought</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -35346,6 +37214,11 @@
 The film primarily appeals to established franchise devotees while delivering the signature torture-porn spectacle new audiences expect from the Saw series.</t>
         </is>
       </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -35436,6 +37309,11 @@
           <t>"Dear David" meets viewer desires for supernatural horror thrills, social media-age scares, and internet folklore brought to life. The film capitalizes on the popularity of the viral Twitter ghost story, appealing to audiences who enjoy creepy online urban legends, jump scares, and paranormal mystery. It satisfies those seeking teen-oriented horror with contemporary digital themes and the tension of being haunted through technology.</t>
         </is>
       </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -35527,6 +37405,11 @@
 "White Bird" meets viewers' desires for an emotionally resonant story about resilience, compassion, and human goodness during difficult times. The film appeals to those seeking an uplifting narrative about courage and kindness, particularly through its Holocaust survival story told from a young person's perspective. It satisfies the need for meaningful family-friendly content that addresses serious historical themes while delivering messages about empathy, standing up against bullying, and the importance of helping others. The film also serves viewers looking for stories that inspire hope and demonstrate the impact of individual acts of bravery.</t>
         </is>
       </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -35618,6 +37501,11 @@
 The film satisfies viewers' desire for **origin stories** by revealing how President Snow became tyrannical, offering psychological depth to a known villain. It meets the need for **moral complexity** through Snow's internal conflict between ambition and compassion, avoiding simple good-vs-evil narratives. Fans gain **franchise expansion** that enriches the Hunger Games universe with backstory about the Games' evolution and Panem's history. The film provides **spectacle and entertainment** through elaborate Games sequences and period-appropriate production design. It explores **relevant themes** about power, propaganda, and authoritarianism that resonate with contemporary political concerns. The romantic subplot and Lucy Gray's musical performances offer **emotional engagement**, while the prequel format gives audiences **nostalgia** for the original series with fresh perspective. Finally, it satisfies curiosity about **world-building details** like the origins of key Hunger Games traditions and the Capitol's post-war society.</t>
         </is>
       </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -35709,6 +37597,11 @@
 "Silent Night" meets viewers' desires for cathartic emotional release through its apocalyptic premise where characters face humanity's final hours. The film satisfies needs for dark comedy that processes collective anxiety about existential threats, offers escapist fantasy about confronting mortality with loved ones, and provides commentary on contemporary social issues like climate change and class dynamics. It appeals to audiences seeking unconventional holiday fare that subverts traditional festive film expectations while exploring themes of grief, acceptance, and human connection in crisis.</t>
         </is>
       </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -35788,6 +37681,11 @@
 *American Dream: The 21 Savage Story* meets viewers' desires for authentic storytelling about immigration, identity, and resilience. The documentary satisfies curiosity about 21 Savage's hidden past as an undocumented British immigrant, providing insight into his journey from Atlanta's streets to hip-hop stardom. It appeals to fans seeking deeper understanding of his music's origins, addresses interests in immigration issues and the American Dream narrative, and fulfills needs for inspirational stories about overcoming adversity and transformation.</t>
         </is>
       </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -35878,6 +37776,11 @@
           <t>"Miller's Girl" appeals to viewers interested in psychological drama and forbidden relationships, particularly those drawn to stories exploring power dynamics, literary themes, and morally complex situations. The film meets desires for provocative content that examines manipulation, ambition, and the blurred lines between mentorship and attraction, while also appealing to audiences who enjoy cerebral narratives centered on writing and intellectual games.</t>
         </is>
       </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -35965,6 +37868,11 @@
 The film "Float" meets viewers' desires for representation and acceptance by portraying a family with a child who has supernatural abilities as a metaphor for disability or neurodivergence. It addresses needs for stories about parental unconditional love, overcoming shame about differences, and community acceptance. The short film resonates with audiences seeking authentic portrayals of the challenges families face when a child doesn't fit societal norms, while offering an emotionally satisfying message about embracing uniqueness and finding belonging despite initial fear of judgment.</t>
         </is>
       </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -36061,6 +37969,11 @@
 - **Familiar genre comfort**: Delivering expected Blumhouse-style horror conventions for fans of mainstream horror entertainment</t>
         </is>
       </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -36147,6 +38060,11 @@
           <t>"Cash Out" meets viewer desires for action-packed entertainment, featuring high-stakes heist thrills, tension, and excitement. It appeals to audiences seeking adrenaline-fueled escapism with elements of crime drama, suspense, and the vicarious thrill of watching elaborate criminal schemes unfold. The film satisfies the appetite for fast-paced storytelling with conflicts between criminals and law enforcement.</t>
         </is>
       </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -36237,6 +38155,11 @@
           <t># The Strangers: Chapter 1 - Viewer Needs Met
 **The Strangers: Chapter 1** satisfies several key viewer desires:
 **Thrill and Adrenaline**: The film delivers intense scares and suspense through its home invasion premise, providing visceral fear and excitement. **Cathartic Fear**: It offers a safe way to experience primal fears of vulnerability and invasion in one's own space. **Escapism**: The horror narrative provides an immersive distraction from everyday life through its tense, atmospheric storytelling. **Pattern Recognition**: Fans of the franchise get familiar slasher/horror tropes while experiencing a new iteration of the story. **Social Experience**: The film creates opportunities for shared viewing experiences, bonding over reactions to scares, and post-viewing discussion. **Morbid Curiosity**: It explores dark "what if" scenarios about random violence and human cruelty in a fictional context.</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -36336,6 +38259,11 @@
 - **Simple adventure storytelling** with treasure-hunting and misfit-team dynamics that don't require deep emotional investment</t>
         </is>
       </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -36428,6 +38356,11 @@
 **Action and Suspense**: Intense heist thriller set during the LA riots provides adrenaline and excitement through high-stakes robberies and dangerous situations. **Historical Context**: Satisfies interest in exploring the 1992 LA riots following the Rodney King verdict, offering a dramatic lens on a significant historical moment. **Father-Son Drama**: Fulfills emotional needs through the central relationship between Tyson Frazier and his son, exploring themes of redemption and family bonds. **Social Commentary**: Addresses desires for films that engage with racial injustice, systemic inequality, and urban unrest in America. **Escapism with Substance**: Combines entertaining genre filmmaking with meaningful subject matter, allowing viewers to engage with serious themes through an accessible action framework.</t>
         </is>
       </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -36518,6 +38451,11 @@
           <t>"The Killer's Game" meets viewers' desires for high-octane action entertainment, featuring intense fight sequences, dark humor, and a revenge-driven plot. It appeals to audiences seeking adrenaline-fueled escapism with a charismatic lead (Dave Bautista), stylized violence, and a mix of thriller elements with comedic moments. The film satisfies fans of assassin/hitman genre conventions while offering straightforward popcorn entertainment without demanding deep emotional investment.</t>
         </is>
       </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -36610,6 +38548,11 @@
 **Survival Thriller Appeal**: Meets the need for suspense and tension through its post-apocalyptic setting where a mother and her sons must stay tethered to their home to survive mysterious evil forces. **Psychological Horror**: Appeals to viewers seeking atmospheric dread and ambiguity about whether supernatural threats are real or manifestations of trauma and paranoia. **Family Drama**: Addresses emotional needs through exploring maternal protection, parent-child bonds under extreme stress, and generational trauma. **Moral Complexity**: Engages viewers who appreciate narratives questioning reality, trust, and whether protective measures become harmful when taken to extremes. **Halle Berry's Performance**: Satisfies fans seeking a strong lead performance in an intense, physically and emotionally demanding role.</t>
         </is>
       </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -36694,6 +38637,11 @@
       <c r="X404" t="inlineStr">
         <is>
           <t>"Bagman" (2024) meets viewers' desires for supernatural horror thrills, tapping into childhood fears through its premise of a malevolent creature that kidnaps children by hiding in bags. The film satisfies needs for suspense, jump scares, and dark atmospheric tension while exploring parental anxiety and trauma. It appeals to horror fans seeking creature-feature entertainment with psychological elements rooted in folklore and nightmares.</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -36793,6 +38741,11 @@
 6. **Feel-Good Resolution** - Delivers the satisfying, uplifting ending audiences expect from holiday films, affirming themes of compassion, inclusion, and community</t>
         </is>
       </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -36882,6 +38835,11 @@
         <is>
           <t># Viewer Desires Met by Den of Thieves 2: Pantera
 The film satisfies audiences seeking high-octane action and heist thrills with elaborate robbery sequences and intense gunfights. It appeals to fans of the original who want continuation of Big Nick's story, while delivering masculine, tough-guy dynamics and crime underworld authenticity. The European setting (diamond heist in the Riviera) provides exotic locales and spectacle. Viewers get straightforward entertainment without complex plotting—a testosterone-fueled popcorn movie with clear good-vs-bad tensions, strategic cat-and-mouse games, and the visceral satisfaction of watching professional criminals execute daring plans with violence and swagger.</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -36982,6 +38940,11 @@
 The film primarily caters to action movie enthusiasts looking for adrenaline-driven entertainment rather than complex character studies or innovative storytelling.</t>
         </is>
       </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -37072,6 +39035,11 @@
           <t>"The Unbreakable Boy" meets viewers' desires for inspirational true stories about overcoming adversity, faith-based content that affirms religious values, and heartwarming family narratives. It appeals to those seeking uplifting stories about parental love, acceptance of children with disabilities, and the triumph of the human spirit against medical and personal challenges. The film satisfies audiences looking for emotional, feel-good cinema that reinforces themes of hope, resilience, and unconditional love.</t>
         </is>
       </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -37146,6 +39114,11 @@
           <t>"The Power of Chi" meets viewers' desires for learning about alternative health practices, understanding traditional Chinese medicine concepts, exploring mind-body connections, and discovering techniques for stress reduction and personal wellness through the ancient practice of chi/qi energy cultivation.</t>
         </is>
       </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -37236,6 +39209,11 @@
           <t>"A Simple Favor" meets viewers' desires for stylish escapism, plot twists, and dark comedy. It appeals to those seeking a glamorous thriller with unexpected turns, morally ambiguous characters, and a mix of mystery and humor. The film satisfies audiences looking for female-driven narratives that blend suspense with satire, offering both entertainment and social commentary on friendship, motherhood, and class differences.</t>
         </is>
       </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -37332,6 +39310,11 @@
 The film provides accessible, adrenaline-fueled entertainment for audiences wanting uncomplicated action without demanding complex character development or moral ambiguity.</t>
         </is>
       </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -37422,6 +39405,11 @@
           <t>"Ballerina" meets viewers' desires for revenge-driven action, emotional catharsis through a grieving protagonist's journey, stylized combat sequences, and themes of friendship and loyalty. The film appeals to audiences seeking a female-led action thriller with visceral fight choreography, a motivated heroine pursuing justice for her friend's death, and the satisfaction of watching an underdog transform into a skilled assassin to punish those responsible for tragedy.</t>
         </is>
       </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -37510,6 +39498,11 @@
       <c r="X413" t="inlineStr">
         <is>
           <t>"The Long Walk" meets viewers' desires for intense psychological tension, dystopian social commentary, and exploration of human endurance under extreme conditions. It satisfies needs for suspenseful entertainment, reflection on authoritarianism and societal control, and emotional catharsis through its portrayal of survival, competition, and the bonds formed under life-or-death circumstances.</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -37610,6 +39603,11 @@
 The film primarily appeals to horror enthusiasts seeking straightforward, anxiety-inducing entertainment.</t>
         </is>
       </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -37696,6 +39694,11 @@
           <t>"Good Fortune" meets viewers' desires for understanding global inequality, development ethics, and the human impact of well-intentioned aid programs. The documentary satisfies needs for critical examination of Western charity efforts in developing countries, revealing unintended consequences of development projects in Kenya. It appeals to audiences seeking thought-provoking content about poverty, displacement, and the complex relationship between donors and recipients, while challenging assumptions about what constitutes "helping" impoverished communities.</t>
         </is>
       </c>
+      <c r="Y415" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -37784,6 +39787,11 @@
       <c r="X416" t="inlineStr">
         <is>
           <t>"Anniversary" (assuming you're referring to the 1968 British dark comedy "The Anniversary") meets viewer desires for dark humor, psychological drama, and campy theatricality. The film satisfies audiences seeking twisted family dynamics, strong performances (particularly Bette Davis's over-the-top portrayal of a domineering mother), and Gothic melodrama that blends horror elements with black comedy. It appeals to those who enjoy uncomfortable character studies and subversive takes on family relationships.</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -37885,6 +39893,11 @@
 The film functions as a "brain candy" thriller that makes audiences feel smart while delivering flashy entertainment.</t>
         </is>
       </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -37977,6 +39990,11 @@
 **Psychological Thriller Appeal**: The film delivers suspense and unpredictability through its portrayal of obsession, manipulation, and domestic terror. **Social Commentary**: It addresses class conflict, sexual politics, and the anxieties of upward mobility in modernizing Korea, resonating with viewers interested in societal critique. **Transgressive Entertainment**: The film's provocative content—adultery, violence, and moral corruption—offers forbidden pleasures and shocking twists. **Aesthetic Experience**: Kim's expressionistic style, claustrophobic mise-en-scène, and melodramatic excess provide a visually striking, artistically ambitious experience. **Cathartic Release**: The escalating chaos and tragic conclusion allow viewers to experience intense emotions safely, exploring fears about domestic stability and sexual temptation.</t>
         </is>
       </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -38067,6 +40085,11 @@
           <t>I don't have reliable information about "Greenland 2: Migration" as it either hasn't been released yet or doesn't exist in my training data (which has a knowledge cutoff date). I cannot provide an accurate summary of what viewer desires or needs this specific film meets without confirmed details about its content, themes, and reception.</t>
         </is>
       </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -38157,6 +40180,11 @@
           <t># The Strangers: Chapter 3 - Viewer Desires Met
 The film satisfies several key audience desires:
 **Primal fear and suspense** - The home invasion premise taps into fundamental anxieties about safety and vulnerability in familiar spaces. **Adrenaline rush** - Jump scares, tension, and violent confrontations provide visceral thrills and excitement. **Cathartic experience** - Watching characters face extreme danger allows viewers to experience fear in a controlled, safe environment. **Mystery and unpredictability** - The masked strangers' motivations and randomness create unsettling uncertainty that keeps audiences engaged. **Escapism** - The horror spectacle offers a departure from everyday life into an intense fictional scenario. **Franchise continuation** - For existing fans, it provides closure or continuation of a familiar horror series they've invested in.</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -38257,6 +40285,11 @@
 The film meets needs for uplifting, lighthearted entertainment with spiritual undertones without being preachy.</t>
         </is>
       </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -38343,6 +40376,11 @@
           <t>I don't have information about "The Hunger Games: Sunrise on the Reaping" as a released film. This appears to be an announced upcoming prequel in The Hunger Games franchise, set during the 50th Hunger Games (Haymitch's Games), but it hasn't been released yet. Without seeing the actual film, I cannot accurately assess what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
